--- a/Results_all_wikiart/Correct_painter_prompt/result_All.xlsx
+++ b/Results_all_wikiart/Correct_painter_prompt/result_All.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LLM_artist_code\Result_all\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI_impostors\Results_all_wikiart\Correct_painter_prompt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{899F5BE5-AC69-4D0F-AC62-AC001CF7284D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C1B6AAA-4C10-41EF-8237-C095EFF0558D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Gemma3" sheetId="1" r:id="rId1"/>
     <sheet name="GPT4.1-mini" sheetId="2" r:id="rId2"/>
     <sheet name="Qwen2.5" sheetId="3" r:id="rId3"/>
+    <sheet name="Phi-4" sheetId="4" r:id="rId4"/>
+    <sheet name="Pixtral" sheetId="5" r:id="rId5"/>
+    <sheet name="LLaMa3.2" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="133">
   <si>
     <t>artist</t>
   </si>
@@ -514,7 +517,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -523,6 +526,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -8212,4 +8218,7385 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA5A9522-5E79-44BC-9A14-024F20E88F66}">
+  <dimension ref="A1:E129"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3">
+        <v>644</v>
+      </c>
+      <c r="C2" s="3">
+        <v>51</v>
+      </c>
+      <c r="D2" s="3">
+        <f>B2/(B2+C2)</f>
+        <v>0.92661870503597121</v>
+      </c>
+      <c r="E2" s="3">
+        <f>B2+C2</f>
+        <v>695</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>230</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <f t="shared" ref="D3:D66" si="0">B3/(B3+C3)</f>
+        <v>1</v>
+      </c>
+      <c r="E3" s="3">
+        <f t="shared" ref="E3:E66" si="1">B3+C3</f>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3">
+        <v>331</v>
+      </c>
+      <c r="C4" s="3">
+        <v>133</v>
+      </c>
+      <c r="D4" s="3">
+        <f t="shared" si="0"/>
+        <v>0.71336206896551724</v>
+      </c>
+      <c r="E4" s="3">
+        <f t="shared" si="1"/>
+        <v>464</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="3">
+        <v>283</v>
+      </c>
+      <c r="C5" s="3">
+        <v>61</v>
+      </c>
+      <c r="D5" s="3">
+        <f t="shared" si="0"/>
+        <v>0.82267441860465118</v>
+      </c>
+      <c r="E5" s="3">
+        <f t="shared" si="1"/>
+        <v>344</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="3">
+        <v>53</v>
+      </c>
+      <c r="C6" s="3">
+        <v>54</v>
+      </c>
+      <c r="D6" s="3">
+        <f t="shared" si="0"/>
+        <v>0.49532710280373832</v>
+      </c>
+      <c r="E6" s="3">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3">
+        <v>147</v>
+      </c>
+      <c r="C7" s="3">
+        <v>16</v>
+      </c>
+      <c r="D7" s="3">
+        <f t="shared" si="0"/>
+        <v>0.90184049079754602</v>
+      </c>
+      <c r="E7" s="3">
+        <f t="shared" si="1"/>
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3">
+        <v>170</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <f t="shared" si="1"/>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="3">
+        <v>96</v>
+      </c>
+      <c r="C9" s="3">
+        <v>65</v>
+      </c>
+      <c r="D9" s="3">
+        <f t="shared" si="0"/>
+        <v>0.59627329192546585</v>
+      </c>
+      <c r="E9" s="3">
+        <f t="shared" si="1"/>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="3">
+        <v>159</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2</v>
+      </c>
+      <c r="D10" s="3">
+        <f t="shared" si="0"/>
+        <v>0.98757763975155277</v>
+      </c>
+      <c r="E10" s="3">
+        <f t="shared" si="1"/>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="3">
+        <v>169</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2</v>
+      </c>
+      <c r="D11" s="3">
+        <f t="shared" si="0"/>
+        <v>0.98830409356725146</v>
+      </c>
+      <c r="E11" s="3">
+        <f t="shared" si="1"/>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="3">
+        <v>223</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2</v>
+      </c>
+      <c r="D12" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99111111111111116</v>
+      </c>
+      <c r="E12" s="3">
+        <f t="shared" si="1"/>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="3">
+        <v>630</v>
+      </c>
+      <c r="C13" s="3">
+        <v>3</v>
+      </c>
+      <c r="D13" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99526066350710896</v>
+      </c>
+      <c r="E13" s="3">
+        <f t="shared" si="1"/>
+        <v>633</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="3">
+        <v>414</v>
+      </c>
+      <c r="C14" s="3">
+        <v>42</v>
+      </c>
+      <c r="D14" s="3">
+        <f t="shared" si="0"/>
+        <v>0.90789473684210531</v>
+      </c>
+      <c r="E14" s="3">
+        <f t="shared" si="1"/>
+        <v>456</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="3">
+        <v>783</v>
+      </c>
+      <c r="C15" s="3">
+        <v>104</v>
+      </c>
+      <c r="D15" s="3">
+        <f t="shared" si="0"/>
+        <v>0.88275084554678696</v>
+      </c>
+      <c r="E15" s="3">
+        <f t="shared" si="1"/>
+        <v>887</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="3">
+        <v>3</v>
+      </c>
+      <c r="C16" s="3">
+        <v>39</v>
+      </c>
+      <c r="D16" s="3">
+        <f t="shared" si="0"/>
+        <v>7.1428571428571425E-2</v>
+      </c>
+      <c r="E16" s="3">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="3">
+        <v>457</v>
+      </c>
+      <c r="C17" s="3">
+        <v>93</v>
+      </c>
+      <c r="D17" s="3">
+        <f t="shared" si="0"/>
+        <v>0.83090909090909093</v>
+      </c>
+      <c r="E17" s="3">
+        <f t="shared" si="1"/>
+        <v>550</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1002</v>
+      </c>
+      <c r="C18" s="3">
+        <v>332</v>
+      </c>
+      <c r="D18" s="3">
+        <f t="shared" si="0"/>
+        <v>0.75112443778110949</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" si="1"/>
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="3">
+        <v>87</v>
+      </c>
+      <c r="C19" s="3">
+        <v>52</v>
+      </c>
+      <c r="D19" s="3">
+        <f t="shared" si="0"/>
+        <v>0.62589928057553956</v>
+      </c>
+      <c r="E19" s="3">
+        <f t="shared" si="1"/>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="3">
+        <v>235</v>
+      </c>
+      <c r="C20" s="3">
+        <v>13</v>
+      </c>
+      <c r="D20" s="3">
+        <f t="shared" si="0"/>
+        <v>0.94758064516129037</v>
+      </c>
+      <c r="E20" s="3">
+        <f t="shared" si="1"/>
+        <v>248</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="3">
+        <v>518</v>
+      </c>
+      <c r="C21" s="3">
+        <v>93</v>
+      </c>
+      <c r="D21" s="3">
+        <f t="shared" si="0"/>
+        <v>0.84779050736497541</v>
+      </c>
+      <c r="E21" s="3">
+        <f t="shared" si="1"/>
+        <v>611</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="3">
+        <v>214</v>
+      </c>
+      <c r="C22" s="3">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E22" s="3">
+        <f t="shared" si="1"/>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="3">
+        <v>51</v>
+      </c>
+      <c r="C23" s="3">
+        <v>159</v>
+      </c>
+      <c r="D23" s="3">
+        <f t="shared" si="0"/>
+        <v>0.24285714285714285</v>
+      </c>
+      <c r="E23" s="3">
+        <f t="shared" si="1"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="3">
+        <v>72</v>
+      </c>
+      <c r="C24" s="3">
+        <v>78</v>
+      </c>
+      <c r="D24" s="3">
+        <f t="shared" si="0"/>
+        <v>0.48</v>
+      </c>
+      <c r="E24" s="3">
+        <f t="shared" si="1"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="3">
+        <v>68</v>
+      </c>
+      <c r="C25" s="3">
+        <v>16</v>
+      </c>
+      <c r="D25" s="3">
+        <f t="shared" si="0"/>
+        <v>0.80952380952380953</v>
+      </c>
+      <c r="E25" s="3">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="3">
+        <v>125</v>
+      </c>
+      <c r="C26" s="3">
+        <v>101</v>
+      </c>
+      <c r="D26" s="3">
+        <f t="shared" si="0"/>
+        <v>0.55309734513274333</v>
+      </c>
+      <c r="E26" s="3">
+        <f t="shared" si="1"/>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="3">
+        <v>51</v>
+      </c>
+      <c r="C27" s="3">
+        <v>108</v>
+      </c>
+      <c r="D27" s="3">
+        <f t="shared" si="0"/>
+        <v>0.32075471698113206</v>
+      </c>
+      <c r="E27" s="3">
+        <f t="shared" si="1"/>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="3">
+        <v>338</v>
+      </c>
+      <c r="C28" s="3">
+        <v>2</v>
+      </c>
+      <c r="D28" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99411764705882355</v>
+      </c>
+      <c r="E28" s="3">
+        <f t="shared" si="1"/>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="3">
+        <v>553</v>
+      </c>
+      <c r="C29" s="3">
+        <v>2</v>
+      </c>
+      <c r="D29" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99639639639639643</v>
+      </c>
+      <c r="E29" s="3">
+        <f t="shared" si="1"/>
+        <v>555</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="3">
+        <v>23</v>
+      </c>
+      <c r="C30" s="3">
+        <v>52</v>
+      </c>
+      <c r="D30" s="3">
+        <f t="shared" si="0"/>
+        <v>0.30666666666666664</v>
+      </c>
+      <c r="E30" s="3">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="3">
+        <v>145</v>
+      </c>
+      <c r="C31" s="3">
+        <v>24</v>
+      </c>
+      <c r="D31" s="3">
+        <f t="shared" si="0"/>
+        <v>0.85798816568047342</v>
+      </c>
+      <c r="E31" s="3">
+        <f t="shared" si="1"/>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="3">
+        <v>197</v>
+      </c>
+      <c r="C32" s="3">
+        <v>7</v>
+      </c>
+      <c r="D32" s="3">
+        <f t="shared" si="0"/>
+        <v>0.96568627450980393</v>
+      </c>
+      <c r="E32" s="3">
+        <f t="shared" si="1"/>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="3">
+        <v>214</v>
+      </c>
+      <c r="C33" s="3">
+        <v>9</v>
+      </c>
+      <c r="D33" s="3">
+        <f t="shared" si="0"/>
+        <v>0.95964125560538116</v>
+      </c>
+      <c r="E33" s="3">
+        <f t="shared" si="1"/>
+        <v>223</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="3">
+        <v>40</v>
+      </c>
+      <c r="C34" s="3">
+        <v>111</v>
+      </c>
+      <c r="D34" s="3">
+        <f t="shared" si="0"/>
+        <v>0.26490066225165565</v>
+      </c>
+      <c r="E34" s="3">
+        <f t="shared" si="1"/>
+        <v>151</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="3">
+        <v>100</v>
+      </c>
+      <c r="C35" s="3">
+        <v>67</v>
+      </c>
+      <c r="D35" s="3">
+        <f t="shared" si="0"/>
+        <v>0.59880239520958078</v>
+      </c>
+      <c r="E35" s="3">
+        <f t="shared" si="1"/>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="3">
+        <v>14</v>
+      </c>
+      <c r="C36" s="3">
+        <v>191</v>
+      </c>
+      <c r="D36" s="3">
+        <f t="shared" si="0"/>
+        <v>6.8292682926829273E-2</v>
+      </c>
+      <c r="E36" s="3">
+        <f t="shared" si="1"/>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="3">
+        <v>84</v>
+      </c>
+      <c r="C37" s="3">
+        <v>92</v>
+      </c>
+      <c r="D37" s="3">
+        <f t="shared" si="0"/>
+        <v>0.47727272727272729</v>
+      </c>
+      <c r="E37" s="3">
+        <f t="shared" si="1"/>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="3">
+        <v>109</v>
+      </c>
+      <c r="C38" s="3">
+        <v>46</v>
+      </c>
+      <c r="D38" s="3">
+        <f t="shared" si="0"/>
+        <v>0.70322580645161292</v>
+      </c>
+      <c r="E38" s="3">
+        <f t="shared" si="1"/>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="3">
+        <v>174</v>
+      </c>
+      <c r="C39" s="3">
+        <v>34</v>
+      </c>
+      <c r="D39" s="3">
+        <f t="shared" si="0"/>
+        <v>0.83653846153846156</v>
+      </c>
+      <c r="E39" s="3">
+        <f t="shared" si="1"/>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="3">
+        <v>141</v>
+      </c>
+      <c r="C40" s="3">
+        <v>21</v>
+      </c>
+      <c r="D40" s="3">
+        <f t="shared" si="0"/>
+        <v>0.87037037037037035</v>
+      </c>
+      <c r="E40" s="3">
+        <f t="shared" si="1"/>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="3">
+        <v>185</v>
+      </c>
+      <c r="C41" s="3">
+        <v>40</v>
+      </c>
+      <c r="D41" s="3">
+        <f t="shared" si="0"/>
+        <v>0.82222222222222219</v>
+      </c>
+      <c r="E41" s="3">
+        <f t="shared" si="1"/>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="3">
+        <v>104</v>
+      </c>
+      <c r="C42" s="3">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99047619047619051</v>
+      </c>
+      <c r="E42" s="3">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="3">
+        <v>142</v>
+      </c>
+      <c r="C43" s="3">
+        <v>40</v>
+      </c>
+      <c r="D43" s="3">
+        <f t="shared" si="0"/>
+        <v>0.78021978021978022</v>
+      </c>
+      <c r="E43" s="3">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="3">
+        <v>77</v>
+      </c>
+      <c r="C44" s="3">
+        <v>140</v>
+      </c>
+      <c r="D44" s="3">
+        <f t="shared" si="0"/>
+        <v>0.35483870967741937</v>
+      </c>
+      <c r="E44" s="3">
+        <f t="shared" si="1"/>
+        <v>217</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" s="3">
+        <v>279</v>
+      </c>
+      <c r="C45" s="3">
+        <v>474</v>
+      </c>
+      <c r="D45" s="3">
+        <f t="shared" si="0"/>
+        <v>0.37051792828685259</v>
+      </c>
+      <c r="E45" s="3">
+        <f t="shared" si="1"/>
+        <v>753</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" s="3">
+        <v>256</v>
+      </c>
+      <c r="C46" s="3">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E46" s="3">
+        <f t="shared" si="1"/>
+        <v>256</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" s="3">
+        <v>72</v>
+      </c>
+      <c r="C47" s="3">
+        <v>11</v>
+      </c>
+      <c r="D47" s="3">
+        <f t="shared" si="0"/>
+        <v>0.86746987951807231</v>
+      </c>
+      <c r="E47" s="3">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" s="3">
+        <v>99</v>
+      </c>
+      <c r="C48" s="3">
+        <v>22</v>
+      </c>
+      <c r="D48" s="3">
+        <f t="shared" si="0"/>
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="E48" s="3">
+        <f t="shared" si="1"/>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" s="3">
+        <v>150</v>
+      </c>
+      <c r="C49" s="3">
+        <v>1</v>
+      </c>
+      <c r="D49" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99337748344370858</v>
+      </c>
+      <c r="E49" s="3">
+        <f t="shared" si="1"/>
+        <v>151</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B50" s="3">
+        <v>295</v>
+      </c>
+      <c r="C50" s="3">
+        <v>29</v>
+      </c>
+      <c r="D50" s="3">
+        <f t="shared" si="0"/>
+        <v>0.91049382716049387</v>
+      </c>
+      <c r="E50" s="3">
+        <f t="shared" si="1"/>
+        <v>324</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51" s="3">
+        <v>104</v>
+      </c>
+      <c r="C51" s="3">
+        <v>1</v>
+      </c>
+      <c r="D51" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99047619047619051</v>
+      </c>
+      <c r="E51" s="3">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B52" s="3">
+        <v>138</v>
+      </c>
+      <c r="C52" s="3">
+        <v>2</v>
+      </c>
+      <c r="D52" s="3">
+        <f t="shared" si="0"/>
+        <v>0.98571428571428577</v>
+      </c>
+      <c r="E52" s="3">
+        <f t="shared" si="1"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B53" s="3">
+        <v>379</v>
+      </c>
+      <c r="C53" s="3">
+        <v>36</v>
+      </c>
+      <c r="D53" s="3">
+        <f t="shared" si="0"/>
+        <v>0.91325301204819276</v>
+      </c>
+      <c r="E53" s="3">
+        <f t="shared" si="1"/>
+        <v>415</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54" s="3">
+        <v>177</v>
+      </c>
+      <c r="C54" s="3">
+        <v>5</v>
+      </c>
+      <c r="D54" s="3">
+        <f t="shared" si="0"/>
+        <v>0.97252747252747251</v>
+      </c>
+      <c r="E54" s="3">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B55" s="3">
+        <v>193</v>
+      </c>
+      <c r="C55" s="3">
+        <v>0</v>
+      </c>
+      <c r="D55" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E55" s="3">
+        <f t="shared" si="1"/>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56" s="3">
+        <v>526</v>
+      </c>
+      <c r="C56" s="3">
+        <v>13</v>
+      </c>
+      <c r="D56" s="3">
+        <f t="shared" si="0"/>
+        <v>0.97588126159554733</v>
+      </c>
+      <c r="E56" s="3">
+        <f t="shared" si="1"/>
+        <v>539</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B57" s="3">
+        <v>346</v>
+      </c>
+      <c r="C57" s="3">
+        <v>78</v>
+      </c>
+      <c r="D57" s="3">
+        <f t="shared" si="0"/>
+        <v>0.81603773584905659</v>
+      </c>
+      <c r="E57" s="3">
+        <f t="shared" si="1"/>
+        <v>424</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B58" s="3">
+        <v>561</v>
+      </c>
+      <c r="C58" s="3">
+        <v>16</v>
+      </c>
+      <c r="D58" s="3">
+        <f t="shared" si="0"/>
+        <v>0.97227036395147315</v>
+      </c>
+      <c r="E58" s="3">
+        <f t="shared" si="1"/>
+        <v>577</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B59" s="3">
+        <v>133</v>
+      </c>
+      <c r="C59" s="3">
+        <v>38</v>
+      </c>
+      <c r="D59" s="3">
+        <f t="shared" si="0"/>
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="E59" s="3">
+        <f t="shared" si="1"/>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B60" s="3">
+        <v>151</v>
+      </c>
+      <c r="C60" s="3">
+        <v>3</v>
+      </c>
+      <c r="D60" s="3">
+        <f t="shared" si="0"/>
+        <v>0.98051948051948057</v>
+      </c>
+      <c r="E60" s="3">
+        <f t="shared" si="1"/>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B61" s="3">
+        <v>515</v>
+      </c>
+      <c r="C61" s="3">
+        <v>5</v>
+      </c>
+      <c r="D61" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99038461538461542</v>
+      </c>
+      <c r="E61" s="3">
+        <f t="shared" si="1"/>
+        <v>520</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B62" s="3">
+        <v>76</v>
+      </c>
+      <c r="C62" s="3">
+        <v>15</v>
+      </c>
+      <c r="D62" s="3">
+        <f t="shared" si="0"/>
+        <v>0.8351648351648352</v>
+      </c>
+      <c r="E62" s="3">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B63" s="3">
+        <v>88</v>
+      </c>
+      <c r="C63" s="3">
+        <v>6</v>
+      </c>
+      <c r="D63" s="3">
+        <f t="shared" si="0"/>
+        <v>0.93617021276595747</v>
+      </c>
+      <c r="E63" s="3">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B64" s="3">
+        <v>106</v>
+      </c>
+      <c r="C64" s="3">
+        <v>28</v>
+      </c>
+      <c r="D64" s="3">
+        <f t="shared" si="0"/>
+        <v>0.79104477611940294</v>
+      </c>
+      <c r="E64" s="3">
+        <f t="shared" si="1"/>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B65" s="3">
+        <v>336</v>
+      </c>
+      <c r="C65" s="3">
+        <v>5</v>
+      </c>
+      <c r="D65" s="3">
+        <f t="shared" si="0"/>
+        <v>0.98533724340175954</v>
+      </c>
+      <c r="E65" s="3">
+        <f t="shared" si="1"/>
+        <v>341</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B66" s="3">
+        <v>123</v>
+      </c>
+      <c r="C66" s="3">
+        <v>44</v>
+      </c>
+      <c r="D66" s="3">
+        <f t="shared" si="0"/>
+        <v>0.73652694610778446</v>
+      </c>
+      <c r="E66" s="3">
+        <f t="shared" si="1"/>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B67" s="3">
+        <v>16</v>
+      </c>
+      <c r="C67" s="3">
+        <v>319</v>
+      </c>
+      <c r="D67" s="3">
+        <f t="shared" ref="D67:D129" si="2">B67/(B67+C67)</f>
+        <v>4.7761194029850747E-2</v>
+      </c>
+      <c r="E67" s="3">
+        <f t="shared" ref="E67:E129" si="3">B67+C67</f>
+        <v>335</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B68" s="3">
+        <v>214</v>
+      </c>
+      <c r="C68" s="3">
+        <v>0</v>
+      </c>
+      <c r="D68" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E68" s="3">
+        <f t="shared" si="3"/>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B69" s="3">
+        <v>434</v>
+      </c>
+      <c r="C69" s="3">
+        <v>350</v>
+      </c>
+      <c r="D69" s="3">
+        <f t="shared" si="2"/>
+        <v>0.5535714285714286</v>
+      </c>
+      <c r="E69" s="3">
+        <f t="shared" si="3"/>
+        <v>784</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B70" s="3">
+        <v>133</v>
+      </c>
+      <c r="C70" s="3">
+        <v>2</v>
+      </c>
+      <c r="D70" s="3">
+        <f t="shared" si="2"/>
+        <v>0.98518518518518516</v>
+      </c>
+      <c r="E70" s="3">
+        <f t="shared" si="3"/>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B71" s="3">
+        <v>200</v>
+      </c>
+      <c r="C71" s="3">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E71" s="3">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B72" s="3">
+        <v>158</v>
+      </c>
+      <c r="C72" s="3">
+        <v>38</v>
+      </c>
+      <c r="D72" s="3">
+        <f t="shared" si="2"/>
+        <v>0.80612244897959184</v>
+      </c>
+      <c r="E72" s="3">
+        <f t="shared" si="3"/>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B73" s="3">
+        <v>135</v>
+      </c>
+      <c r="C73" s="3">
+        <v>10</v>
+      </c>
+      <c r="D73" s="3">
+        <f t="shared" si="2"/>
+        <v>0.93103448275862066</v>
+      </c>
+      <c r="E73" s="3">
+        <f t="shared" si="3"/>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B74" s="3">
+        <v>166</v>
+      </c>
+      <c r="C74" s="3">
+        <v>5</v>
+      </c>
+      <c r="D74" s="3">
+        <f t="shared" si="2"/>
+        <v>0.9707602339181286</v>
+      </c>
+      <c r="E74" s="3">
+        <f t="shared" si="3"/>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B75" s="3">
+        <v>84</v>
+      </c>
+      <c r="C75" s="3">
+        <v>1</v>
+      </c>
+      <c r="D75" s="3">
+        <f t="shared" si="2"/>
+        <v>0.9882352941176471</v>
+      </c>
+      <c r="E75" s="3">
+        <f t="shared" si="3"/>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B76" s="3">
+        <v>247</v>
+      </c>
+      <c r="C76" s="3">
+        <v>0</v>
+      </c>
+      <c r="D76" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E76" s="3">
+        <f t="shared" si="3"/>
+        <v>247</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B77" s="3">
+        <v>319</v>
+      </c>
+      <c r="C77" s="3">
+        <v>5</v>
+      </c>
+      <c r="D77" s="3">
+        <f t="shared" si="2"/>
+        <v>0.98456790123456794</v>
+      </c>
+      <c r="E77" s="3">
+        <f t="shared" si="3"/>
+        <v>324</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B78" s="3">
+        <v>140</v>
+      </c>
+      <c r="C78" s="3">
+        <v>54</v>
+      </c>
+      <c r="D78" s="3">
+        <f t="shared" si="2"/>
+        <v>0.72164948453608246</v>
+      </c>
+      <c r="E78" s="3">
+        <f t="shared" si="3"/>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B79" s="3">
+        <v>154</v>
+      </c>
+      <c r="C79" s="3">
+        <v>51</v>
+      </c>
+      <c r="D79" s="3">
+        <f t="shared" si="2"/>
+        <v>0.75121951219512195</v>
+      </c>
+      <c r="E79" s="3">
+        <f t="shared" si="3"/>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B80" s="3">
+        <v>55</v>
+      </c>
+      <c r="C80" s="3">
+        <v>109</v>
+      </c>
+      <c r="D80" s="3">
+        <f t="shared" si="2"/>
+        <v>0.33536585365853661</v>
+      </c>
+      <c r="E80" s="3">
+        <f t="shared" si="3"/>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B81" s="3">
+        <v>176</v>
+      </c>
+      <c r="C81" s="3">
+        <v>3</v>
+      </c>
+      <c r="D81" s="3">
+        <f t="shared" si="2"/>
+        <v>0.98324022346368711</v>
+      </c>
+      <c r="E81" s="3">
+        <f t="shared" si="3"/>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B82" s="3">
+        <v>56</v>
+      </c>
+      <c r="C82" s="3">
+        <v>178</v>
+      </c>
+      <c r="D82" s="3">
+        <f t="shared" si="2"/>
+        <v>0.23931623931623933</v>
+      </c>
+      <c r="E82" s="3">
+        <f t="shared" si="3"/>
+        <v>234</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B83" s="3">
+        <v>49</v>
+      </c>
+      <c r="C83" s="3">
+        <v>77</v>
+      </c>
+      <c r="D83" s="3">
+        <f t="shared" si="2"/>
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="E83" s="3">
+        <f t="shared" si="3"/>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B84" s="3">
+        <v>680</v>
+      </c>
+      <c r="C84" s="3">
+        <v>85</v>
+      </c>
+      <c r="D84" s="3">
+        <f t="shared" si="2"/>
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="E84" s="3">
+        <f t="shared" si="3"/>
+        <v>765</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B85" s="3">
+        <v>574</v>
+      </c>
+      <c r="C85" s="3">
+        <v>1</v>
+      </c>
+      <c r="D85" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99826086956521742</v>
+      </c>
+      <c r="E85" s="3">
+        <f t="shared" si="3"/>
+        <v>575</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B86" s="3">
+        <v>264</v>
+      </c>
+      <c r="C86" s="3">
+        <v>29</v>
+      </c>
+      <c r="D86" s="3">
+        <f t="shared" si="2"/>
+        <v>0.90102389078498291</v>
+      </c>
+      <c r="E86" s="3">
+        <f t="shared" si="3"/>
+        <v>293</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B87" s="3">
+        <v>362</v>
+      </c>
+      <c r="C87" s="3">
+        <v>0</v>
+      </c>
+      <c r="D87" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E87" s="3">
+        <f t="shared" si="3"/>
+        <v>362</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B88" s="3">
+        <v>119</v>
+      </c>
+      <c r="C88" s="3">
+        <v>0</v>
+      </c>
+      <c r="D88" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E88" s="3">
+        <f t="shared" si="3"/>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B89" s="3">
+        <v>10</v>
+      </c>
+      <c r="C89" s="3">
+        <v>119</v>
+      </c>
+      <c r="D89" s="3">
+        <f t="shared" si="2"/>
+        <v>7.7519379844961239E-2</v>
+      </c>
+      <c r="E89" s="3">
+        <f t="shared" si="3"/>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B90" s="3">
+        <v>43</v>
+      </c>
+      <c r="C90" s="3">
+        <v>5</v>
+      </c>
+      <c r="D90" s="3">
+        <f t="shared" si="2"/>
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="E90" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B91" s="3">
+        <v>36</v>
+      </c>
+      <c r="C91" s="3">
+        <v>59</v>
+      </c>
+      <c r="D91" s="3">
+        <f t="shared" si="2"/>
+        <v>0.37894736842105264</v>
+      </c>
+      <c r="E91" s="3">
+        <f t="shared" si="3"/>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B92" s="3">
+        <v>142</v>
+      </c>
+      <c r="C92" s="3">
+        <v>7</v>
+      </c>
+      <c r="D92" s="3">
+        <f t="shared" si="2"/>
+        <v>0.95302013422818788</v>
+      </c>
+      <c r="E92" s="3">
+        <f t="shared" si="3"/>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B93" s="3">
+        <v>1729</v>
+      </c>
+      <c r="C93" s="3">
+        <v>90</v>
+      </c>
+      <c r="D93" s="3">
+        <f t="shared" si="2"/>
+        <v>0.95052226498075865</v>
+      </c>
+      <c r="E93" s="3">
+        <f t="shared" si="3"/>
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B94" s="3">
+        <v>104</v>
+      </c>
+      <c r="C94" s="3">
+        <v>9</v>
+      </c>
+      <c r="D94" s="3">
+        <f t="shared" si="2"/>
+        <v>0.92035398230088494</v>
+      </c>
+      <c r="E94" s="3">
+        <f t="shared" si="3"/>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B95" s="3">
+        <v>197</v>
+      </c>
+      <c r="C95" s="3">
+        <v>1</v>
+      </c>
+      <c r="D95" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99494949494949492</v>
+      </c>
+      <c r="E95" s="3">
+        <f t="shared" si="3"/>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B96" s="3">
+        <v>129</v>
+      </c>
+      <c r="C96" s="3">
+        <v>35</v>
+      </c>
+      <c r="D96" s="3">
+        <f t="shared" si="2"/>
+        <v>0.78658536585365857</v>
+      </c>
+      <c r="E96" s="3">
+        <f t="shared" si="3"/>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B97" s="3">
+        <v>214</v>
+      </c>
+      <c r="C97" s="3">
+        <v>2</v>
+      </c>
+      <c r="D97" s="3">
+        <f t="shared" si="2"/>
+        <v>0.9907407407407407</v>
+      </c>
+      <c r="E97" s="3">
+        <f t="shared" si="3"/>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B98" s="3">
+        <v>143</v>
+      </c>
+      <c r="C98" s="3">
+        <v>619</v>
+      </c>
+      <c r="D98" s="3">
+        <f t="shared" si="2"/>
+        <v>0.18766404199475065</v>
+      </c>
+      <c r="E98" s="3">
+        <f t="shared" si="3"/>
+        <v>762</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B99" s="3">
+        <v>117</v>
+      </c>
+      <c r="C99" s="3">
+        <v>13</v>
+      </c>
+      <c r="D99" s="3">
+        <f t="shared" si="2"/>
+        <v>0.9</v>
+      </c>
+      <c r="E99" s="3">
+        <f t="shared" si="3"/>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B100" s="3">
+        <v>483</v>
+      </c>
+      <c r="C100" s="3">
+        <v>96</v>
+      </c>
+      <c r="D100" s="3">
+        <f t="shared" si="2"/>
+        <v>0.83419689119170981</v>
+      </c>
+      <c r="E100" s="3">
+        <f t="shared" si="3"/>
+        <v>579</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B101" s="3">
+        <v>246</v>
+      </c>
+      <c r="C101" s="3">
+        <v>113</v>
+      </c>
+      <c r="D101" s="3">
+        <f t="shared" si="2"/>
+        <v>0.68523676880222839</v>
+      </c>
+      <c r="E101" s="3">
+        <f t="shared" si="3"/>
+        <v>359</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B102" s="3">
+        <v>180</v>
+      </c>
+      <c r="C102" s="3">
+        <v>79</v>
+      </c>
+      <c r="D102" s="3">
+        <f t="shared" si="2"/>
+        <v>0.69498069498069504</v>
+      </c>
+      <c r="E102" s="3">
+        <f t="shared" si="3"/>
+        <v>259</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B103" s="3">
+        <v>1356</v>
+      </c>
+      <c r="C103" s="3">
+        <v>44</v>
+      </c>
+      <c r="D103" s="3">
+        <f t="shared" si="2"/>
+        <v>0.96857142857142853</v>
+      </c>
+      <c r="E103" s="3">
+        <f t="shared" si="3"/>
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B104" s="3">
+        <v>136</v>
+      </c>
+      <c r="C104" s="3">
+        <v>6</v>
+      </c>
+      <c r="D104" s="3">
+        <f t="shared" si="2"/>
+        <v>0.95774647887323938</v>
+      </c>
+      <c r="E104" s="3">
+        <f t="shared" si="3"/>
+        <v>142</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B105" s="3">
+        <v>158</v>
+      </c>
+      <c r="C105" s="3">
+        <v>15</v>
+      </c>
+      <c r="D105" s="3">
+        <f t="shared" si="2"/>
+        <v>0.91329479768786126</v>
+      </c>
+      <c r="E105" s="3">
+        <f t="shared" si="3"/>
+        <v>173</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B106" s="3">
+        <v>914</v>
+      </c>
+      <c r="C106" s="3">
+        <v>5</v>
+      </c>
+      <c r="D106" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99455930359085964</v>
+      </c>
+      <c r="E106" s="3">
+        <f t="shared" si="3"/>
+        <v>919</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B107" s="3">
+        <v>131</v>
+      </c>
+      <c r="C107" s="3">
+        <v>2</v>
+      </c>
+      <c r="D107" s="3">
+        <f t="shared" si="2"/>
+        <v>0.98496240601503759</v>
+      </c>
+      <c r="E107" s="3">
+        <f t="shared" si="3"/>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B108" s="3">
+        <v>108</v>
+      </c>
+      <c r="C108" s="3">
+        <v>35</v>
+      </c>
+      <c r="D108" s="3">
+        <f t="shared" si="2"/>
+        <v>0.75524475524475521</v>
+      </c>
+      <c r="E108" s="3">
+        <f t="shared" si="3"/>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B109" s="3">
+        <v>439</v>
+      </c>
+      <c r="C109" s="3">
+        <v>77</v>
+      </c>
+      <c r="D109" s="3">
+        <f t="shared" si="2"/>
+        <v>0.85077519379844957</v>
+      </c>
+      <c r="E109" s="3">
+        <f t="shared" si="3"/>
+        <v>516</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B110" s="3">
+        <v>295</v>
+      </c>
+      <c r="C110" s="3">
+        <v>481</v>
+      </c>
+      <c r="D110" s="3">
+        <f t="shared" si="2"/>
+        <v>0.38015463917525771</v>
+      </c>
+      <c r="E110" s="3">
+        <f t="shared" si="3"/>
+        <v>776</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B111" s="3">
+        <v>119</v>
+      </c>
+      <c r="C111" s="3">
+        <v>360</v>
+      </c>
+      <c r="D111" s="3">
+        <f t="shared" si="2"/>
+        <v>0.24843423799582465</v>
+      </c>
+      <c r="E111" s="3">
+        <f t="shared" si="3"/>
+        <v>479</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B112" s="3">
+        <v>229</v>
+      </c>
+      <c r="C112" s="3">
+        <v>88</v>
+      </c>
+      <c r="D112" s="3">
+        <f t="shared" si="2"/>
+        <v>0.72239747634069396</v>
+      </c>
+      <c r="E112" s="3">
+        <f t="shared" si="3"/>
+        <v>317</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B113" s="3">
+        <v>144</v>
+      </c>
+      <c r="C113" s="3">
+        <v>22</v>
+      </c>
+      <c r="D113" s="3">
+        <f t="shared" si="2"/>
+        <v>0.86746987951807231</v>
+      </c>
+      <c r="E113" s="3">
+        <f t="shared" si="3"/>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B114" s="3">
+        <v>165</v>
+      </c>
+      <c r="C114" s="3">
+        <v>4</v>
+      </c>
+      <c r="D114" s="3">
+        <f t="shared" si="2"/>
+        <v>0.97633136094674555</v>
+      </c>
+      <c r="E114" s="3">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B115" s="3">
+        <v>163</v>
+      </c>
+      <c r="C115" s="3">
+        <v>77</v>
+      </c>
+      <c r="D115" s="3">
+        <f t="shared" si="2"/>
+        <v>0.6791666666666667</v>
+      </c>
+      <c r="E115" s="3">
+        <f t="shared" si="3"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B116" s="3">
+        <v>127</v>
+      </c>
+      <c r="C116" s="3">
+        <v>37</v>
+      </c>
+      <c r="D116" s="3">
+        <f t="shared" si="2"/>
+        <v>0.77439024390243905</v>
+      </c>
+      <c r="E116" s="3">
+        <f t="shared" si="3"/>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B117" s="3">
+        <v>102</v>
+      </c>
+      <c r="C117" s="3">
+        <v>85</v>
+      </c>
+      <c r="D117" s="3">
+        <f t="shared" si="2"/>
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="E117" s="3">
+        <f t="shared" si="3"/>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B118" s="3">
+        <v>153</v>
+      </c>
+      <c r="C118" s="3">
+        <v>51</v>
+      </c>
+      <c r="D118" s="3">
+        <f t="shared" si="2"/>
+        <v>0.75</v>
+      </c>
+      <c r="E118" s="3">
+        <f t="shared" si="3"/>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B119" s="3">
+        <v>199</v>
+      </c>
+      <c r="C119" s="3">
+        <v>0</v>
+      </c>
+      <c r="D119" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E119" s="3">
+        <f t="shared" si="3"/>
+        <v>199</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B120" s="3">
+        <v>172</v>
+      </c>
+      <c r="C120" s="3">
+        <v>19</v>
+      </c>
+      <c r="D120" s="3">
+        <f t="shared" si="2"/>
+        <v>0.90052356020942403</v>
+      </c>
+      <c r="E120" s="3">
+        <f t="shared" si="3"/>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B121" s="3">
+        <v>174</v>
+      </c>
+      <c r="C121" s="3">
+        <v>4</v>
+      </c>
+      <c r="D121" s="3">
+        <f t="shared" si="2"/>
+        <v>0.97752808988764039</v>
+      </c>
+      <c r="E121" s="3">
+        <f t="shared" si="3"/>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B122" s="3">
+        <v>216</v>
+      </c>
+      <c r="C122" s="3">
+        <v>9</v>
+      </c>
+      <c r="D122" s="3">
+        <f t="shared" si="2"/>
+        <v>0.96</v>
+      </c>
+      <c r="E122" s="3">
+        <f t="shared" si="3"/>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B123" s="3">
+        <v>231</v>
+      </c>
+      <c r="C123" s="3">
+        <v>7</v>
+      </c>
+      <c r="D123" s="3">
+        <f t="shared" si="2"/>
+        <v>0.97058823529411764</v>
+      </c>
+      <c r="E123" s="3">
+        <f t="shared" si="3"/>
+        <v>238</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B124" s="3">
+        <v>129</v>
+      </c>
+      <c r="C124" s="3">
+        <v>37</v>
+      </c>
+      <c r="D124" s="3">
+        <f t="shared" si="2"/>
+        <v>0.77710843373493976</v>
+      </c>
+      <c r="E124" s="3">
+        <f t="shared" si="3"/>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B125" s="3">
+        <v>101</v>
+      </c>
+      <c r="C125" s="3">
+        <v>31</v>
+      </c>
+      <c r="D125" s="3">
+        <f t="shared" si="2"/>
+        <v>0.76515151515151514</v>
+      </c>
+      <c r="E125" s="3">
+        <f t="shared" si="3"/>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B126" s="3">
+        <v>229</v>
+      </c>
+      <c r="C126" s="3">
+        <v>1660</v>
+      </c>
+      <c r="D126" s="3">
+        <f t="shared" si="2"/>
+        <v>0.1212281630492324</v>
+      </c>
+      <c r="E126" s="3">
+        <f t="shared" si="3"/>
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B127" s="3">
+        <v>348</v>
+      </c>
+      <c r="C127" s="3">
+        <v>6</v>
+      </c>
+      <c r="D127" s="3">
+        <f t="shared" si="2"/>
+        <v>0.98305084745762716</v>
+      </c>
+      <c r="E127" s="3">
+        <f t="shared" si="3"/>
+        <v>354</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B128" s="3">
+        <v>137</v>
+      </c>
+      <c r="C128" s="3">
+        <v>4</v>
+      </c>
+      <c r="D128" s="3">
+        <f t="shared" si="2"/>
+        <v>0.97163120567375882</v>
+      </c>
+      <c r="E128" s="3">
+        <f t="shared" si="3"/>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B129" s="3">
+        <v>318</v>
+      </c>
+      <c r="C129" s="3">
+        <v>11</v>
+      </c>
+      <c r="D129" s="3">
+        <f t="shared" si="2"/>
+        <v>0.96656534954407292</v>
+      </c>
+      <c r="E129" s="3">
+        <f t="shared" si="3"/>
+        <v>329</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E35507B9-3217-4D92-BDC1-B53C47948D57}">
+  <dimension ref="A1:E129"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3">
+        <v>609</v>
+      </c>
+      <c r="C2" s="3">
+        <v>86</v>
+      </c>
+      <c r="D2" s="3">
+        <f>B2/(B2+C2)</f>
+        <v>0.87625899280575537</v>
+      </c>
+      <c r="E2" s="3">
+        <f>B2+C2</f>
+        <v>695</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>230</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <f t="shared" ref="D3:D66" si="0">B3/(B3+C3)</f>
+        <v>1</v>
+      </c>
+      <c r="E3" s="3">
+        <f t="shared" ref="E3:E66" si="1">B3+C3</f>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3">
+        <v>464</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E4" s="3">
+        <f t="shared" si="1"/>
+        <v>464</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="3">
+        <v>339</v>
+      </c>
+      <c r="C5" s="3">
+        <v>5</v>
+      </c>
+      <c r="D5" s="3">
+        <f t="shared" si="0"/>
+        <v>0.98546511627906974</v>
+      </c>
+      <c r="E5" s="3">
+        <f t="shared" si="1"/>
+        <v>344</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="3">
+        <v>104</v>
+      </c>
+      <c r="C6" s="3">
+        <v>3</v>
+      </c>
+      <c r="D6" s="3">
+        <f t="shared" si="0"/>
+        <v>0.9719626168224299</v>
+      </c>
+      <c r="E6" s="3">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3">
+        <v>162</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99386503067484666</v>
+      </c>
+      <c r="E7" s="3">
+        <f t="shared" si="1"/>
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3">
+        <v>170</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <f t="shared" si="1"/>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="3">
+        <v>159</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2</v>
+      </c>
+      <c r="D9" s="3">
+        <f t="shared" si="0"/>
+        <v>0.98757763975155277</v>
+      </c>
+      <c r="E9" s="3">
+        <f t="shared" si="1"/>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="3">
+        <v>159</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2</v>
+      </c>
+      <c r="D10" s="3">
+        <f t="shared" si="0"/>
+        <v>0.98757763975155277</v>
+      </c>
+      <c r="E10" s="3">
+        <f t="shared" si="1"/>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="3">
+        <v>146</v>
+      </c>
+      <c r="C11" s="3">
+        <v>25</v>
+      </c>
+      <c r="D11" s="3">
+        <f t="shared" si="0"/>
+        <v>0.85380116959064323</v>
+      </c>
+      <c r="E11" s="3">
+        <f t="shared" si="1"/>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="3">
+        <v>224</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99555555555555553</v>
+      </c>
+      <c r="E12" s="3">
+        <f t="shared" si="1"/>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="3">
+        <v>581</v>
+      </c>
+      <c r="C13" s="3">
+        <v>52</v>
+      </c>
+      <c r="D13" s="3">
+        <f t="shared" si="0"/>
+        <v>0.91785150078988942</v>
+      </c>
+      <c r="E13" s="3">
+        <f t="shared" si="1"/>
+        <v>633</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="3">
+        <v>443</v>
+      </c>
+      <c r="C14" s="3">
+        <v>13</v>
+      </c>
+      <c r="D14" s="3">
+        <f t="shared" si="0"/>
+        <v>0.97149122807017541</v>
+      </c>
+      <c r="E14" s="3">
+        <f t="shared" si="1"/>
+        <v>456</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="3">
+        <v>882</v>
+      </c>
+      <c r="C15" s="3">
+        <v>5</v>
+      </c>
+      <c r="D15" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99436302142051858</v>
+      </c>
+      <c r="E15" s="3">
+        <f t="shared" si="1"/>
+        <v>887</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="3">
+        <v>40</v>
+      </c>
+      <c r="C16" s="3">
+        <v>2</v>
+      </c>
+      <c r="D16" s="3">
+        <f t="shared" si="0"/>
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="E16" s="3">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="3">
+        <v>550</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E17" s="3">
+        <f t="shared" si="1"/>
+        <v>550</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1330</v>
+      </c>
+      <c r="C18" s="3">
+        <v>4</v>
+      </c>
+      <c r="D18" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99700149925037485</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" si="1"/>
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="3">
+        <v>133</v>
+      </c>
+      <c r="C19" s="3">
+        <v>6</v>
+      </c>
+      <c r="D19" s="3">
+        <f t="shared" si="0"/>
+        <v>0.95683453237410077</v>
+      </c>
+      <c r="E19" s="3">
+        <f t="shared" si="1"/>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="3">
+        <v>247</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99596774193548387</v>
+      </c>
+      <c r="E20" s="3">
+        <f t="shared" si="1"/>
+        <v>248</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="3">
+        <v>591</v>
+      </c>
+      <c r="C21" s="3">
+        <v>20</v>
+      </c>
+      <c r="D21" s="3">
+        <f t="shared" si="0"/>
+        <v>0.96726677577741405</v>
+      </c>
+      <c r="E21" s="3">
+        <f t="shared" si="1"/>
+        <v>611</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="3">
+        <v>214</v>
+      </c>
+      <c r="C22" s="3">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E22" s="3">
+        <f t="shared" si="1"/>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="3">
+        <v>209</v>
+      </c>
+      <c r="C23" s="3">
+        <v>1</v>
+      </c>
+      <c r="D23" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99523809523809526</v>
+      </c>
+      <c r="E23" s="3">
+        <f t="shared" si="1"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="3">
+        <v>135</v>
+      </c>
+      <c r="C24" s="3">
+        <v>15</v>
+      </c>
+      <c r="D24" s="3">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+      <c r="E24" s="3">
+        <f t="shared" si="1"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="3">
+        <v>79</v>
+      </c>
+      <c r="C25" s="3">
+        <v>5</v>
+      </c>
+      <c r="D25" s="3">
+        <f t="shared" si="0"/>
+        <v>0.94047619047619047</v>
+      </c>
+      <c r="E25" s="3">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="3">
+        <v>225</v>
+      </c>
+      <c r="C26" s="3">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99557522123893805</v>
+      </c>
+      <c r="E26" s="3">
+        <f t="shared" si="1"/>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="3">
+        <v>155</v>
+      </c>
+      <c r="C27" s="3">
+        <v>4</v>
+      </c>
+      <c r="D27" s="3">
+        <f t="shared" si="0"/>
+        <v>0.97484276729559749</v>
+      </c>
+      <c r="E27" s="3">
+        <f t="shared" si="1"/>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="3">
+        <v>338</v>
+      </c>
+      <c r="C28" s="3">
+        <v>2</v>
+      </c>
+      <c r="D28" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99411764705882355</v>
+      </c>
+      <c r="E28" s="3">
+        <f t="shared" si="1"/>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="3">
+        <v>555</v>
+      </c>
+      <c r="C29" s="3">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E29" s="3">
+        <f t="shared" si="1"/>
+        <v>555</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="3">
+        <v>72</v>
+      </c>
+      <c r="C30" s="3">
+        <v>3</v>
+      </c>
+      <c r="D30" s="3">
+        <f t="shared" si="0"/>
+        <v>0.96</v>
+      </c>
+      <c r="E30" s="3">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="3">
+        <v>161</v>
+      </c>
+      <c r="C31" s="3">
+        <v>8</v>
+      </c>
+      <c r="D31" s="3">
+        <f t="shared" si="0"/>
+        <v>0.9526627218934911</v>
+      </c>
+      <c r="E31" s="3">
+        <f t="shared" si="1"/>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="3">
+        <v>172</v>
+      </c>
+      <c r="C32" s="3">
+        <v>32</v>
+      </c>
+      <c r="D32" s="3">
+        <f t="shared" si="0"/>
+        <v>0.84313725490196079</v>
+      </c>
+      <c r="E32" s="3">
+        <f t="shared" si="1"/>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="3">
+        <v>213</v>
+      </c>
+      <c r="C33" s="3">
+        <v>10</v>
+      </c>
+      <c r="D33" s="3">
+        <f t="shared" si="0"/>
+        <v>0.95515695067264572</v>
+      </c>
+      <c r="E33" s="3">
+        <f t="shared" si="1"/>
+        <v>223</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="3">
+        <v>144</v>
+      </c>
+      <c r="C34" s="3">
+        <v>7</v>
+      </c>
+      <c r="D34" s="3">
+        <f t="shared" si="0"/>
+        <v>0.95364238410596025</v>
+      </c>
+      <c r="E34" s="3">
+        <f t="shared" si="1"/>
+        <v>151</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="3">
+        <v>165</v>
+      </c>
+      <c r="C35" s="3">
+        <v>2</v>
+      </c>
+      <c r="D35" s="3">
+        <f t="shared" si="0"/>
+        <v>0.9880239520958084</v>
+      </c>
+      <c r="E35" s="3">
+        <f t="shared" si="1"/>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="3">
+        <v>200</v>
+      </c>
+      <c r="C36" s="3">
+        <v>5</v>
+      </c>
+      <c r="D36" s="3">
+        <f t="shared" si="0"/>
+        <v>0.97560975609756095</v>
+      </c>
+      <c r="E36" s="3">
+        <f t="shared" si="1"/>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="3">
+        <v>176</v>
+      </c>
+      <c r="C37" s="3">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E37" s="3">
+        <f t="shared" si="1"/>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="3">
+        <v>136</v>
+      </c>
+      <c r="C38" s="3">
+        <v>19</v>
+      </c>
+      <c r="D38" s="3">
+        <f t="shared" si="0"/>
+        <v>0.8774193548387097</v>
+      </c>
+      <c r="E38" s="3">
+        <f t="shared" si="1"/>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="3">
+        <v>207</v>
+      </c>
+      <c r="C39" s="3">
+        <v>1</v>
+      </c>
+      <c r="D39" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99519230769230771</v>
+      </c>
+      <c r="E39" s="3">
+        <f t="shared" si="1"/>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="3">
+        <v>157</v>
+      </c>
+      <c r="C40" s="3">
+        <v>5</v>
+      </c>
+      <c r="D40" s="3">
+        <f t="shared" si="0"/>
+        <v>0.96913580246913578</v>
+      </c>
+      <c r="E40" s="3">
+        <f t="shared" si="1"/>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="3">
+        <v>225</v>
+      </c>
+      <c r="C41" s="3">
+        <v>0</v>
+      </c>
+      <c r="D41" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E41" s="3">
+        <f t="shared" si="1"/>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="3">
+        <v>97</v>
+      </c>
+      <c r="C42" s="3">
+        <v>8</v>
+      </c>
+      <c r="D42" s="3">
+        <f t="shared" si="0"/>
+        <v>0.92380952380952386</v>
+      </c>
+      <c r="E42" s="3">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="3">
+        <v>182</v>
+      </c>
+      <c r="C43" s="3">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E43" s="3">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="3">
+        <v>215</v>
+      </c>
+      <c r="C44" s="3">
+        <v>2</v>
+      </c>
+      <c r="D44" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99078341013824889</v>
+      </c>
+      <c r="E44" s="3">
+        <f t="shared" si="1"/>
+        <v>217</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" s="3">
+        <v>753</v>
+      </c>
+      <c r="C45" s="3">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E45" s="3">
+        <f t="shared" si="1"/>
+        <v>753</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" s="3">
+        <v>256</v>
+      </c>
+      <c r="C46" s="3">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E46" s="3">
+        <f t="shared" si="1"/>
+        <v>256</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" s="3">
+        <v>81</v>
+      </c>
+      <c r="C47" s="3">
+        <v>2</v>
+      </c>
+      <c r="D47" s="3">
+        <f t="shared" si="0"/>
+        <v>0.97590361445783136</v>
+      </c>
+      <c r="E47" s="3">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" s="3">
+        <v>105</v>
+      </c>
+      <c r="C48" s="3">
+        <v>16</v>
+      </c>
+      <c r="D48" s="3">
+        <f t="shared" si="0"/>
+        <v>0.86776859504132231</v>
+      </c>
+      <c r="E48" s="3">
+        <f t="shared" si="1"/>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" s="3">
+        <v>150</v>
+      </c>
+      <c r="C49" s="3">
+        <v>1</v>
+      </c>
+      <c r="D49" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99337748344370858</v>
+      </c>
+      <c r="E49" s="3">
+        <f t="shared" si="1"/>
+        <v>151</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B50" s="3">
+        <v>299</v>
+      </c>
+      <c r="C50" s="3">
+        <v>25</v>
+      </c>
+      <c r="D50" s="3">
+        <f t="shared" si="0"/>
+        <v>0.9228395061728395</v>
+      </c>
+      <c r="E50" s="3">
+        <f t="shared" si="1"/>
+        <v>324</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51" s="3">
+        <v>104</v>
+      </c>
+      <c r="C51" s="3">
+        <v>1</v>
+      </c>
+      <c r="D51" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99047619047619051</v>
+      </c>
+      <c r="E51" s="3">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B52" s="3">
+        <v>140</v>
+      </c>
+      <c r="C52" s="3">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E52" s="3">
+        <f t="shared" si="1"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B53" s="3">
+        <v>411</v>
+      </c>
+      <c r="C53" s="3">
+        <v>4</v>
+      </c>
+      <c r="D53" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99036144578313257</v>
+      </c>
+      <c r="E53" s="3">
+        <f t="shared" si="1"/>
+        <v>415</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54" s="3">
+        <v>163</v>
+      </c>
+      <c r="C54" s="3">
+        <v>19</v>
+      </c>
+      <c r="D54" s="3">
+        <f t="shared" si="0"/>
+        <v>0.89560439560439564</v>
+      </c>
+      <c r="E54" s="3">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B55" s="3">
+        <v>190</v>
+      </c>
+      <c r="C55" s="3">
+        <v>3</v>
+      </c>
+      <c r="D55" s="3">
+        <f t="shared" si="0"/>
+        <v>0.98445595854922274</v>
+      </c>
+      <c r="E55" s="3">
+        <f t="shared" si="1"/>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56" s="3">
+        <v>535</v>
+      </c>
+      <c r="C56" s="3">
+        <v>4</v>
+      </c>
+      <c r="D56" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99257884972170685</v>
+      </c>
+      <c r="E56" s="3">
+        <f t="shared" si="1"/>
+        <v>539</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B57" s="3">
+        <v>403</v>
+      </c>
+      <c r="C57" s="3">
+        <v>21</v>
+      </c>
+      <c r="D57" s="3">
+        <f t="shared" si="0"/>
+        <v>0.95047169811320753</v>
+      </c>
+      <c r="E57" s="3">
+        <f t="shared" si="1"/>
+        <v>424</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B58" s="3">
+        <v>568</v>
+      </c>
+      <c r="C58" s="3">
+        <v>9</v>
+      </c>
+      <c r="D58" s="3">
+        <f t="shared" si="0"/>
+        <v>0.98440207972270366</v>
+      </c>
+      <c r="E58" s="3">
+        <f t="shared" si="1"/>
+        <v>577</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B59" s="3">
+        <v>164</v>
+      </c>
+      <c r="C59" s="3">
+        <v>7</v>
+      </c>
+      <c r="D59" s="3">
+        <f t="shared" si="0"/>
+        <v>0.95906432748538006</v>
+      </c>
+      <c r="E59" s="3">
+        <f t="shared" si="1"/>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B60" s="3">
+        <v>153</v>
+      </c>
+      <c r="C60" s="3">
+        <v>1</v>
+      </c>
+      <c r="D60" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99350649350649356</v>
+      </c>
+      <c r="E60" s="3">
+        <f t="shared" si="1"/>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B61" s="3">
+        <v>498</v>
+      </c>
+      <c r="C61" s="3">
+        <v>22</v>
+      </c>
+      <c r="D61" s="3">
+        <f t="shared" si="0"/>
+        <v>0.95769230769230773</v>
+      </c>
+      <c r="E61" s="3">
+        <f t="shared" si="1"/>
+        <v>520</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B62" s="3">
+        <v>91</v>
+      </c>
+      <c r="C62" s="3">
+        <v>0</v>
+      </c>
+      <c r="D62" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E62" s="3">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B63" s="3">
+        <v>94</v>
+      </c>
+      <c r="C63" s="3">
+        <v>0</v>
+      </c>
+      <c r="D63" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E63" s="3">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B64" s="3">
+        <v>132</v>
+      </c>
+      <c r="C64" s="3">
+        <v>2</v>
+      </c>
+      <c r="D64" s="3">
+        <f t="shared" si="0"/>
+        <v>0.9850746268656716</v>
+      </c>
+      <c r="E64" s="3">
+        <f t="shared" si="1"/>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B65" s="3">
+        <v>328</v>
+      </c>
+      <c r="C65" s="3">
+        <v>13</v>
+      </c>
+      <c r="D65" s="3">
+        <f t="shared" si="0"/>
+        <v>0.96187683284457481</v>
+      </c>
+      <c r="E65" s="3">
+        <f t="shared" si="1"/>
+        <v>341</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B66" s="3">
+        <v>161</v>
+      </c>
+      <c r="C66" s="3">
+        <v>6</v>
+      </c>
+      <c r="D66" s="3">
+        <f t="shared" si="0"/>
+        <v>0.9640718562874252</v>
+      </c>
+      <c r="E66" s="3">
+        <f t="shared" si="1"/>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B67" s="3">
+        <v>334</v>
+      </c>
+      <c r="C67" s="3">
+        <v>1</v>
+      </c>
+      <c r="D67" s="3">
+        <f t="shared" ref="D67:D129" si="2">B67/(B67+C67)</f>
+        <v>0.9970149253731343</v>
+      </c>
+      <c r="E67" s="3">
+        <f t="shared" ref="E67:E129" si="3">B67+C67</f>
+        <v>335</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B68" s="3">
+        <v>213</v>
+      </c>
+      <c r="C68" s="3">
+        <v>1</v>
+      </c>
+      <c r="D68" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99532710280373837</v>
+      </c>
+      <c r="E68" s="3">
+        <f t="shared" si="3"/>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B69" s="3">
+        <v>744</v>
+      </c>
+      <c r="C69" s="3">
+        <v>40</v>
+      </c>
+      <c r="D69" s="3">
+        <f t="shared" si="2"/>
+        <v>0.94897959183673475</v>
+      </c>
+      <c r="E69" s="3">
+        <f t="shared" si="3"/>
+        <v>784</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B70" s="3">
+        <v>135</v>
+      </c>
+      <c r="C70" s="3">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E70" s="3">
+        <f t="shared" si="3"/>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B71" s="3">
+        <v>198</v>
+      </c>
+      <c r="C71" s="3">
+        <v>2</v>
+      </c>
+      <c r="D71" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99</v>
+      </c>
+      <c r="E71" s="3">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B72" s="3">
+        <v>196</v>
+      </c>
+      <c r="C72" s="3">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E72" s="3">
+        <f t="shared" si="3"/>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B73" s="3">
+        <v>144</v>
+      </c>
+      <c r="C73" s="3">
+        <v>1</v>
+      </c>
+      <c r="D73" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99310344827586206</v>
+      </c>
+      <c r="E73" s="3">
+        <f t="shared" si="3"/>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B74" s="3">
+        <v>160</v>
+      </c>
+      <c r="C74" s="3">
+        <v>11</v>
+      </c>
+      <c r="D74" s="3">
+        <f t="shared" si="2"/>
+        <v>0.93567251461988299</v>
+      </c>
+      <c r="E74" s="3">
+        <f t="shared" si="3"/>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B75" s="3">
+        <v>83</v>
+      </c>
+      <c r="C75" s="3">
+        <v>2</v>
+      </c>
+      <c r="D75" s="3">
+        <f t="shared" si="2"/>
+        <v>0.97647058823529409</v>
+      </c>
+      <c r="E75" s="3">
+        <f t="shared" si="3"/>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B76" s="3">
+        <v>247</v>
+      </c>
+      <c r="C76" s="3">
+        <v>0</v>
+      </c>
+      <c r="D76" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E76" s="3">
+        <f t="shared" si="3"/>
+        <v>247</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B77" s="3">
+        <v>324</v>
+      </c>
+      <c r="C77" s="3">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E77" s="3">
+        <f t="shared" si="3"/>
+        <v>324</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B78" s="3">
+        <v>188</v>
+      </c>
+      <c r="C78" s="3">
+        <v>6</v>
+      </c>
+      <c r="D78" s="3">
+        <f t="shared" si="2"/>
+        <v>0.96907216494845361</v>
+      </c>
+      <c r="E78" s="3">
+        <f t="shared" si="3"/>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B79" s="3">
+        <v>189</v>
+      </c>
+      <c r="C79" s="3">
+        <v>16</v>
+      </c>
+      <c r="D79" s="3">
+        <f t="shared" si="2"/>
+        <v>0.92195121951219516</v>
+      </c>
+      <c r="E79" s="3">
+        <f t="shared" si="3"/>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B80" s="3">
+        <v>69</v>
+      </c>
+      <c r="C80" s="3">
+        <v>95</v>
+      </c>
+      <c r="D80" s="3">
+        <f t="shared" si="2"/>
+        <v>0.42073170731707316</v>
+      </c>
+      <c r="E80" s="3">
+        <f t="shared" si="3"/>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B81" s="3">
+        <v>179</v>
+      </c>
+      <c r="C81" s="3">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E81" s="3">
+        <f t="shared" si="3"/>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B82" s="3">
+        <v>227</v>
+      </c>
+      <c r="C82" s="3">
+        <v>7</v>
+      </c>
+      <c r="D82" s="3">
+        <f t="shared" si="2"/>
+        <v>0.97008547008547008</v>
+      </c>
+      <c r="E82" s="3">
+        <f t="shared" si="3"/>
+        <v>234</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B83" s="3">
+        <v>87</v>
+      </c>
+      <c r="C83" s="3">
+        <v>39</v>
+      </c>
+      <c r="D83" s="3">
+        <f t="shared" si="2"/>
+        <v>0.69047619047619047</v>
+      </c>
+      <c r="E83" s="3">
+        <f t="shared" si="3"/>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B84" s="3">
+        <v>733</v>
+      </c>
+      <c r="C84" s="3">
+        <v>32</v>
+      </c>
+      <c r="D84" s="3">
+        <f t="shared" si="2"/>
+        <v>0.95816993464052291</v>
+      </c>
+      <c r="E84" s="3">
+        <f t="shared" si="3"/>
+        <v>765</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B85" s="3">
+        <v>573</v>
+      </c>
+      <c r="C85" s="3">
+        <v>2</v>
+      </c>
+      <c r="D85" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99652173913043474</v>
+      </c>
+      <c r="E85" s="3">
+        <f t="shared" si="3"/>
+        <v>575</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B86" s="3">
+        <v>292</v>
+      </c>
+      <c r="C86" s="3">
+        <v>1</v>
+      </c>
+      <c r="D86" s="3">
+        <f t="shared" si="2"/>
+        <v>0.9965870307167235</v>
+      </c>
+      <c r="E86" s="3">
+        <f t="shared" si="3"/>
+        <v>293</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B87" s="3">
+        <v>362</v>
+      </c>
+      <c r="C87" s="3">
+        <v>0</v>
+      </c>
+      <c r="D87" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E87" s="3">
+        <f t="shared" si="3"/>
+        <v>362</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B88" s="3">
+        <v>119</v>
+      </c>
+      <c r="C88" s="3">
+        <v>0</v>
+      </c>
+      <c r="D88" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E88" s="3">
+        <f t="shared" si="3"/>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B89" s="3">
+        <v>118</v>
+      </c>
+      <c r="C89" s="3">
+        <v>11</v>
+      </c>
+      <c r="D89" s="3">
+        <f t="shared" si="2"/>
+        <v>0.9147286821705426</v>
+      </c>
+      <c r="E89" s="3">
+        <f t="shared" si="3"/>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B90" s="3">
+        <v>48</v>
+      </c>
+      <c r="C90" s="3">
+        <v>0</v>
+      </c>
+      <c r="D90" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E90" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B91" s="3">
+        <v>93</v>
+      </c>
+      <c r="C91" s="3">
+        <v>2</v>
+      </c>
+      <c r="D91" s="3">
+        <f t="shared" si="2"/>
+        <v>0.97894736842105268</v>
+      </c>
+      <c r="E91" s="3">
+        <f t="shared" si="3"/>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B92" s="3">
+        <v>149</v>
+      </c>
+      <c r="C92" s="3">
+        <v>0</v>
+      </c>
+      <c r="D92" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E92" s="3">
+        <f t="shared" si="3"/>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B93" s="3">
+        <v>1660</v>
+      </c>
+      <c r="C93" s="3">
+        <v>159</v>
+      </c>
+      <c r="D93" s="3">
+        <f t="shared" si="2"/>
+        <v>0.91258933479934035</v>
+      </c>
+      <c r="E93" s="3">
+        <f t="shared" si="3"/>
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B94" s="3">
+        <v>113</v>
+      </c>
+      <c r="C94" s="3">
+        <v>0</v>
+      </c>
+      <c r="D94" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E94" s="3">
+        <f t="shared" si="3"/>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B95" s="3">
+        <v>198</v>
+      </c>
+      <c r="C95" s="3">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E95" s="3">
+        <f t="shared" si="3"/>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B96" s="3">
+        <v>163</v>
+      </c>
+      <c r="C96" s="3">
+        <v>1</v>
+      </c>
+      <c r="D96" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99390243902439024</v>
+      </c>
+      <c r="E96" s="3">
+        <f t="shared" si="3"/>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B97" s="3">
+        <v>204</v>
+      </c>
+      <c r="C97" s="3">
+        <v>12</v>
+      </c>
+      <c r="D97" s="3">
+        <f t="shared" si="2"/>
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="E97" s="3">
+        <f t="shared" si="3"/>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B98" s="3">
+        <v>708</v>
+      </c>
+      <c r="C98" s="3">
+        <v>54</v>
+      </c>
+      <c r="D98" s="3">
+        <f t="shared" si="2"/>
+        <v>0.92913385826771655</v>
+      </c>
+      <c r="E98" s="3">
+        <f t="shared" si="3"/>
+        <v>762</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B99" s="3">
+        <v>124</v>
+      </c>
+      <c r="C99" s="3">
+        <v>6</v>
+      </c>
+      <c r="D99" s="3">
+        <f t="shared" si="2"/>
+        <v>0.9538461538461539</v>
+      </c>
+      <c r="E99" s="3">
+        <f t="shared" si="3"/>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B100" s="3">
+        <v>574</v>
+      </c>
+      <c r="C100" s="3">
+        <v>5</v>
+      </c>
+      <c r="D100" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99136442141623493</v>
+      </c>
+      <c r="E100" s="3">
+        <f t="shared" si="3"/>
+        <v>579</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B101" s="3">
+        <v>357</v>
+      </c>
+      <c r="C101" s="3">
+        <v>2</v>
+      </c>
+      <c r="D101" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99442896935933145</v>
+      </c>
+      <c r="E101" s="3">
+        <f t="shared" si="3"/>
+        <v>359</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B102" s="3">
+        <v>253</v>
+      </c>
+      <c r="C102" s="3">
+        <v>6</v>
+      </c>
+      <c r="D102" s="3">
+        <f t="shared" si="2"/>
+        <v>0.97683397683397688</v>
+      </c>
+      <c r="E102" s="3">
+        <f t="shared" si="3"/>
+        <v>259</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B103" s="3">
+        <v>1393</v>
+      </c>
+      <c r="C103" s="3">
+        <v>7</v>
+      </c>
+      <c r="D103" s="3">
+        <f t="shared" si="2"/>
+        <v>0.995</v>
+      </c>
+      <c r="E103" s="3">
+        <f t="shared" si="3"/>
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B104" s="3">
+        <v>141</v>
+      </c>
+      <c r="C104" s="3">
+        <v>1</v>
+      </c>
+      <c r="D104" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99295774647887325</v>
+      </c>
+      <c r="E104" s="3">
+        <f t="shared" si="3"/>
+        <v>142</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B105" s="3">
+        <v>173</v>
+      </c>
+      <c r="C105" s="3">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E105" s="3">
+        <f t="shared" si="3"/>
+        <v>173</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B106" s="3">
+        <v>918</v>
+      </c>
+      <c r="C106" s="3">
+        <v>1</v>
+      </c>
+      <c r="D106" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99891186071817195</v>
+      </c>
+      <c r="E106" s="3">
+        <f t="shared" si="3"/>
+        <v>919</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B107" s="3">
+        <v>131</v>
+      </c>
+      <c r="C107" s="3">
+        <v>2</v>
+      </c>
+      <c r="D107" s="3">
+        <f t="shared" si="2"/>
+        <v>0.98496240601503759</v>
+      </c>
+      <c r="E107" s="3">
+        <f t="shared" si="3"/>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B108" s="3">
+        <v>126</v>
+      </c>
+      <c r="C108" s="3">
+        <v>17</v>
+      </c>
+      <c r="D108" s="3">
+        <f t="shared" si="2"/>
+        <v>0.88111888111888115</v>
+      </c>
+      <c r="E108" s="3">
+        <f t="shared" si="3"/>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B109" s="3">
+        <v>357</v>
+      </c>
+      <c r="C109" s="3">
+        <v>159</v>
+      </c>
+      <c r="D109" s="3">
+        <f t="shared" si="2"/>
+        <v>0.69186046511627908</v>
+      </c>
+      <c r="E109" s="3">
+        <f t="shared" si="3"/>
+        <v>516</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B110" s="3">
+        <v>737</v>
+      </c>
+      <c r="C110" s="3">
+        <v>39</v>
+      </c>
+      <c r="D110" s="3">
+        <f t="shared" si="2"/>
+        <v>0.94974226804123707</v>
+      </c>
+      <c r="E110" s="3">
+        <f t="shared" si="3"/>
+        <v>776</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B111" s="3">
+        <v>409</v>
+      </c>
+      <c r="C111" s="3">
+        <v>70</v>
+      </c>
+      <c r="D111" s="3">
+        <f t="shared" si="2"/>
+        <v>0.85386221294363251</v>
+      </c>
+      <c r="E111" s="3">
+        <f t="shared" si="3"/>
+        <v>479</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B112" s="3">
+        <v>310</v>
+      </c>
+      <c r="C112" s="3">
+        <v>7</v>
+      </c>
+      <c r="D112" s="3">
+        <f t="shared" si="2"/>
+        <v>0.97791798107255523</v>
+      </c>
+      <c r="E112" s="3">
+        <f t="shared" si="3"/>
+        <v>317</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B113" s="3">
+        <v>164</v>
+      </c>
+      <c r="C113" s="3">
+        <v>2</v>
+      </c>
+      <c r="D113" s="3">
+        <f t="shared" si="2"/>
+        <v>0.98795180722891562</v>
+      </c>
+      <c r="E113" s="3">
+        <f t="shared" si="3"/>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B114" s="3">
+        <v>169</v>
+      </c>
+      <c r="C114" s="3">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E114" s="3">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B115" s="3">
+        <v>212</v>
+      </c>
+      <c r="C115" s="3">
+        <v>28</v>
+      </c>
+      <c r="D115" s="3">
+        <f t="shared" si="2"/>
+        <v>0.8833333333333333</v>
+      </c>
+      <c r="E115" s="3">
+        <f t="shared" si="3"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B116" s="3">
+        <v>159</v>
+      </c>
+      <c r="C116" s="3">
+        <v>5</v>
+      </c>
+      <c r="D116" s="3">
+        <f t="shared" si="2"/>
+        <v>0.96951219512195119</v>
+      </c>
+      <c r="E116" s="3">
+        <f t="shared" si="3"/>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B117" s="3">
+        <v>179</v>
+      </c>
+      <c r="C117" s="3">
+        <v>8</v>
+      </c>
+      <c r="D117" s="3">
+        <f t="shared" si="2"/>
+        <v>0.95721925133689845</v>
+      </c>
+      <c r="E117" s="3">
+        <f t="shared" si="3"/>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B118" s="3">
+        <v>191</v>
+      </c>
+      <c r="C118" s="3">
+        <v>13</v>
+      </c>
+      <c r="D118" s="3">
+        <f t="shared" si="2"/>
+        <v>0.93627450980392157</v>
+      </c>
+      <c r="E118" s="3">
+        <f t="shared" si="3"/>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B119" s="3">
+        <v>199</v>
+      </c>
+      <c r="C119" s="3">
+        <v>0</v>
+      </c>
+      <c r="D119" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E119" s="3">
+        <f t="shared" si="3"/>
+        <v>199</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B120" s="3">
+        <v>178</v>
+      </c>
+      <c r="C120" s="3">
+        <v>13</v>
+      </c>
+      <c r="D120" s="3">
+        <f t="shared" si="2"/>
+        <v>0.93193717277486909</v>
+      </c>
+      <c r="E120" s="3">
+        <f t="shared" si="3"/>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B121" s="3">
+        <v>171</v>
+      </c>
+      <c r="C121" s="3">
+        <v>7</v>
+      </c>
+      <c r="D121" s="3">
+        <f t="shared" si="2"/>
+        <v>0.9606741573033708</v>
+      </c>
+      <c r="E121" s="3">
+        <f t="shared" si="3"/>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B122" s="3">
+        <v>220</v>
+      </c>
+      <c r="C122" s="3">
+        <v>5</v>
+      </c>
+      <c r="D122" s="3">
+        <f t="shared" si="2"/>
+        <v>0.97777777777777775</v>
+      </c>
+      <c r="E122" s="3">
+        <f t="shared" si="3"/>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B123" s="3">
+        <v>231</v>
+      </c>
+      <c r="C123" s="3">
+        <v>7</v>
+      </c>
+      <c r="D123" s="3">
+        <f t="shared" si="2"/>
+        <v>0.97058823529411764</v>
+      </c>
+      <c r="E123" s="3">
+        <f t="shared" si="3"/>
+        <v>238</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B124" s="3">
+        <v>155</v>
+      </c>
+      <c r="C124" s="3">
+        <v>11</v>
+      </c>
+      <c r="D124" s="3">
+        <f t="shared" si="2"/>
+        <v>0.9337349397590361</v>
+      </c>
+      <c r="E124" s="3">
+        <f t="shared" si="3"/>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B125" s="3">
+        <v>122</v>
+      </c>
+      <c r="C125" s="3">
+        <v>10</v>
+      </c>
+      <c r="D125" s="3">
+        <f t="shared" si="2"/>
+        <v>0.9242424242424242</v>
+      </c>
+      <c r="E125" s="3">
+        <f t="shared" si="3"/>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B126" s="3">
+        <v>1314</v>
+      </c>
+      <c r="C126" s="3">
+        <v>575</v>
+      </c>
+      <c r="D126" s="3">
+        <f t="shared" si="2"/>
+        <v>0.69560614081524619</v>
+      </c>
+      <c r="E126" s="3">
+        <f t="shared" si="3"/>
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B127" s="3">
+        <v>352</v>
+      </c>
+      <c r="C127" s="3">
+        <v>2</v>
+      </c>
+      <c r="D127" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99435028248587576</v>
+      </c>
+      <c r="E127" s="3">
+        <f t="shared" si="3"/>
+        <v>354</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B128" s="3">
+        <v>141</v>
+      </c>
+      <c r="C128" s="3">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E128" s="3">
+        <f t="shared" si="3"/>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B129" s="3">
+        <v>326</v>
+      </c>
+      <c r="C129" s="3">
+        <v>3</v>
+      </c>
+      <c r="D129" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99088145896656532</v>
+      </c>
+      <c r="E129" s="3">
+        <f t="shared" si="3"/>
+        <v>329</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5497304D-8A53-454F-9D4F-C910A77A3327}">
+  <dimension ref="A1:E129"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3">
+        <v>688</v>
+      </c>
+      <c r="C2" s="3">
+        <v>7</v>
+      </c>
+      <c r="D2" s="3">
+        <f>B2/(B2+C2)</f>
+        <v>0.98992805755395685</v>
+      </c>
+      <c r="E2" s="3">
+        <f>B2+C2</f>
+        <v>695</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>230</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <f t="shared" ref="D3:D66" si="0">B3/(B3+C3)</f>
+        <v>1</v>
+      </c>
+      <c r="E3" s="3">
+        <f t="shared" ref="E3:E66" si="1">B3+C3</f>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3">
+        <v>463</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99784482758620685</v>
+      </c>
+      <c r="E4" s="3">
+        <f t="shared" si="1"/>
+        <v>464</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="3">
+        <v>340</v>
+      </c>
+      <c r="C5" s="3">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3">
+        <f t="shared" si="0"/>
+        <v>0.98837209302325579</v>
+      </c>
+      <c r="E5" s="3">
+        <f t="shared" si="1"/>
+        <v>344</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="3">
+        <v>65</v>
+      </c>
+      <c r="C6" s="3">
+        <v>42</v>
+      </c>
+      <c r="D6" s="3">
+        <f t="shared" si="0"/>
+        <v>0.60747663551401865</v>
+      </c>
+      <c r="E6" s="3">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3">
+        <v>140</v>
+      </c>
+      <c r="C7" s="3">
+        <v>23</v>
+      </c>
+      <c r="D7" s="3">
+        <f t="shared" si="0"/>
+        <v>0.85889570552147243</v>
+      </c>
+      <c r="E7" s="3">
+        <f t="shared" si="1"/>
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3">
+        <v>170</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <f t="shared" si="1"/>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="3">
+        <v>160</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99378881987577639</v>
+      </c>
+      <c r="E9" s="3">
+        <f t="shared" si="1"/>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="3">
+        <v>112</v>
+      </c>
+      <c r="C10" s="3">
+        <v>49</v>
+      </c>
+      <c r="D10" s="3">
+        <f t="shared" si="0"/>
+        <v>0.69565217391304346</v>
+      </c>
+      <c r="E10" s="3">
+        <f t="shared" si="1"/>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="3">
+        <v>123</v>
+      </c>
+      <c r="C11" s="3">
+        <v>48</v>
+      </c>
+      <c r="D11" s="3">
+        <f t="shared" si="0"/>
+        <v>0.7192982456140351</v>
+      </c>
+      <c r="E11" s="3">
+        <f t="shared" si="1"/>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="3">
+        <v>224</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99555555555555553</v>
+      </c>
+      <c r="E12" s="3">
+        <f t="shared" si="1"/>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="3">
+        <v>631</v>
+      </c>
+      <c r="C13" s="3">
+        <v>2</v>
+      </c>
+      <c r="D13" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99684044233807267</v>
+      </c>
+      <c r="E13" s="3">
+        <f t="shared" si="1"/>
+        <v>633</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="3">
+        <v>452</v>
+      </c>
+      <c r="C14" s="3">
+        <v>4</v>
+      </c>
+      <c r="D14" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99122807017543857</v>
+      </c>
+      <c r="E14" s="3">
+        <f t="shared" si="1"/>
+        <v>456</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="3">
+        <v>886</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99887260428410374</v>
+      </c>
+      <c r="E15" s="3">
+        <f t="shared" si="1"/>
+        <v>887</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="3">
+        <v>42</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E16" s="3">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="3">
+        <v>549</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99818181818181817</v>
+      </c>
+      <c r="E17" s="3">
+        <f t="shared" si="1"/>
+        <v>550</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1321</v>
+      </c>
+      <c r="C18" s="3">
+        <v>13</v>
+      </c>
+      <c r="D18" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99025487256371814</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" si="1"/>
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="3">
+        <v>135</v>
+      </c>
+      <c r="C19" s="3">
+        <v>4</v>
+      </c>
+      <c r="D19" s="3">
+        <f t="shared" si="0"/>
+        <v>0.97122302158273377</v>
+      </c>
+      <c r="E19" s="3">
+        <f t="shared" si="1"/>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="3">
+        <v>240</v>
+      </c>
+      <c r="C20" s="3">
+        <v>8</v>
+      </c>
+      <c r="D20" s="3">
+        <f t="shared" si="0"/>
+        <v>0.967741935483871</v>
+      </c>
+      <c r="E20" s="3">
+        <f t="shared" si="1"/>
+        <v>248</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="3">
+        <v>605</v>
+      </c>
+      <c r="C21" s="3">
+        <v>6</v>
+      </c>
+      <c r="D21" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99018003273322419</v>
+      </c>
+      <c r="E21" s="3">
+        <f t="shared" si="1"/>
+        <v>611</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="3">
+        <v>213</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99532710280373837</v>
+      </c>
+      <c r="E22" s="3">
+        <f t="shared" si="1"/>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="3">
+        <v>207</v>
+      </c>
+      <c r="C23" s="3">
+        <v>3</v>
+      </c>
+      <c r="D23" s="3">
+        <f t="shared" si="0"/>
+        <v>0.98571428571428577</v>
+      </c>
+      <c r="E23" s="3">
+        <f t="shared" si="1"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="3">
+        <v>137</v>
+      </c>
+      <c r="C24" s="3">
+        <v>13</v>
+      </c>
+      <c r="D24" s="3">
+        <f t="shared" si="0"/>
+        <v>0.91333333333333333</v>
+      </c>
+      <c r="E24" s="3">
+        <f t="shared" si="1"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="3">
+        <v>75</v>
+      </c>
+      <c r="C25" s="3">
+        <v>9</v>
+      </c>
+      <c r="D25" s="3">
+        <f t="shared" si="0"/>
+        <v>0.8928571428571429</v>
+      </c>
+      <c r="E25" s="3">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="3">
+        <v>222</v>
+      </c>
+      <c r="C26" s="3">
+        <v>4</v>
+      </c>
+      <c r="D26" s="3">
+        <f t="shared" si="0"/>
+        <v>0.98230088495575218</v>
+      </c>
+      <c r="E26" s="3">
+        <f t="shared" si="1"/>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="3">
+        <v>143</v>
+      </c>
+      <c r="C27" s="3">
+        <v>16</v>
+      </c>
+      <c r="D27" s="3">
+        <f t="shared" si="0"/>
+        <v>0.89937106918238996</v>
+      </c>
+      <c r="E27" s="3">
+        <f t="shared" si="1"/>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="3">
+        <v>323</v>
+      </c>
+      <c r="C28" s="3">
+        <v>17</v>
+      </c>
+      <c r="D28" s="3">
+        <f t="shared" si="0"/>
+        <v>0.95</v>
+      </c>
+      <c r="E28" s="3">
+        <f t="shared" si="1"/>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="3">
+        <v>555</v>
+      </c>
+      <c r="C29" s="3">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E29" s="3">
+        <f t="shared" si="1"/>
+        <v>555</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="3">
+        <v>58</v>
+      </c>
+      <c r="C30" s="3">
+        <v>17</v>
+      </c>
+      <c r="D30" s="3">
+        <f t="shared" si="0"/>
+        <v>0.77333333333333332</v>
+      </c>
+      <c r="E30" s="3">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="3">
+        <v>115</v>
+      </c>
+      <c r="C31" s="3">
+        <v>54</v>
+      </c>
+      <c r="D31" s="3">
+        <f t="shared" si="0"/>
+        <v>0.68047337278106512</v>
+      </c>
+      <c r="E31" s="3">
+        <f t="shared" si="1"/>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="3">
+        <v>202</v>
+      </c>
+      <c r="C32" s="3">
+        <v>2</v>
+      </c>
+      <c r="D32" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99019607843137258</v>
+      </c>
+      <c r="E32" s="3">
+        <f t="shared" si="1"/>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="3">
+        <v>215</v>
+      </c>
+      <c r="C33" s="3">
+        <v>8</v>
+      </c>
+      <c r="D33" s="3">
+        <f t="shared" si="0"/>
+        <v>0.9641255605381166</v>
+      </c>
+      <c r="E33" s="3">
+        <f t="shared" si="1"/>
+        <v>223</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="3">
+        <v>144</v>
+      </c>
+      <c r="C34" s="3">
+        <v>7</v>
+      </c>
+      <c r="D34" s="3">
+        <f t="shared" si="0"/>
+        <v>0.95364238410596025</v>
+      </c>
+      <c r="E34" s="3">
+        <f t="shared" si="1"/>
+        <v>151</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="3">
+        <v>165</v>
+      </c>
+      <c r="C35" s="3">
+        <v>2</v>
+      </c>
+      <c r="D35" s="3">
+        <f t="shared" si="0"/>
+        <v>0.9880239520958084</v>
+      </c>
+      <c r="E35" s="3">
+        <f t="shared" si="1"/>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="3">
+        <v>176</v>
+      </c>
+      <c r="C36" s="3">
+        <v>29</v>
+      </c>
+      <c r="D36" s="3">
+        <f t="shared" si="0"/>
+        <v>0.85853658536585364</v>
+      </c>
+      <c r="E36" s="3">
+        <f t="shared" si="1"/>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="3">
+        <v>169</v>
+      </c>
+      <c r="C37" s="3">
+        <v>7</v>
+      </c>
+      <c r="D37" s="3">
+        <f t="shared" si="0"/>
+        <v>0.96022727272727271</v>
+      </c>
+      <c r="E37" s="3">
+        <f t="shared" si="1"/>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="3">
+        <v>11</v>
+      </c>
+      <c r="C38" s="3">
+        <v>144</v>
+      </c>
+      <c r="D38" s="3">
+        <f t="shared" si="0"/>
+        <v>7.0967741935483872E-2</v>
+      </c>
+      <c r="E38" s="3">
+        <f t="shared" si="1"/>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="3">
+        <v>200</v>
+      </c>
+      <c r="C39" s="3">
+        <v>8</v>
+      </c>
+      <c r="D39" s="3">
+        <f t="shared" si="0"/>
+        <v>0.96153846153846156</v>
+      </c>
+      <c r="E39" s="3">
+        <f t="shared" si="1"/>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="3">
+        <v>159</v>
+      </c>
+      <c r="C40" s="3">
+        <v>3</v>
+      </c>
+      <c r="D40" s="3">
+        <f t="shared" si="0"/>
+        <v>0.98148148148148151</v>
+      </c>
+      <c r="E40" s="3">
+        <f t="shared" si="1"/>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="3">
+        <v>215</v>
+      </c>
+      <c r="C41" s="3">
+        <v>10</v>
+      </c>
+      <c r="D41" s="3">
+        <f t="shared" si="0"/>
+        <v>0.9555555555555556</v>
+      </c>
+      <c r="E41" s="3">
+        <f t="shared" si="1"/>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="3">
+        <v>101</v>
+      </c>
+      <c r="C42" s="3">
+        <v>4</v>
+      </c>
+      <c r="D42" s="3">
+        <f t="shared" si="0"/>
+        <v>0.96190476190476193</v>
+      </c>
+      <c r="E42" s="3">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="3">
+        <v>182</v>
+      </c>
+      <c r="C43" s="3">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E43" s="3">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="3">
+        <v>214</v>
+      </c>
+      <c r="C44" s="3">
+        <v>3</v>
+      </c>
+      <c r="D44" s="3">
+        <f t="shared" si="0"/>
+        <v>0.98617511520737322</v>
+      </c>
+      <c r="E44" s="3">
+        <f t="shared" si="1"/>
+        <v>217</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" s="3">
+        <v>741</v>
+      </c>
+      <c r="C45" s="3">
+        <v>12</v>
+      </c>
+      <c r="D45" s="3">
+        <f t="shared" si="0"/>
+        <v>0.98406374501992033</v>
+      </c>
+      <c r="E45" s="3">
+        <f t="shared" si="1"/>
+        <v>753</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" s="3">
+        <v>256</v>
+      </c>
+      <c r="C46" s="3">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E46" s="3">
+        <f t="shared" si="1"/>
+        <v>256</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" s="3">
+        <v>79</v>
+      </c>
+      <c r="C47" s="3">
+        <v>4</v>
+      </c>
+      <c r="D47" s="3">
+        <f t="shared" si="0"/>
+        <v>0.95180722891566261</v>
+      </c>
+      <c r="E47" s="3">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" s="3">
+        <v>109</v>
+      </c>
+      <c r="C48" s="3">
+        <v>12</v>
+      </c>
+      <c r="D48" s="3">
+        <f t="shared" si="0"/>
+        <v>0.90082644628099173</v>
+      </c>
+      <c r="E48" s="3">
+        <f t="shared" si="1"/>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" s="3">
+        <v>143</v>
+      </c>
+      <c r="C49" s="3">
+        <v>8</v>
+      </c>
+      <c r="D49" s="3">
+        <f t="shared" si="0"/>
+        <v>0.94701986754966883</v>
+      </c>
+      <c r="E49" s="3">
+        <f t="shared" si="1"/>
+        <v>151</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B50" s="3">
+        <v>322</v>
+      </c>
+      <c r="C50" s="3">
+        <v>2</v>
+      </c>
+      <c r="D50" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99382716049382713</v>
+      </c>
+      <c r="E50" s="3">
+        <f t="shared" si="1"/>
+        <v>324</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51" s="3">
+        <v>105</v>
+      </c>
+      <c r="C51" s="3">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E51" s="3">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B52" s="3">
+        <v>140</v>
+      </c>
+      <c r="C52" s="3">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E52" s="3">
+        <f t="shared" si="1"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B53" s="3">
+        <v>405</v>
+      </c>
+      <c r="C53" s="3">
+        <v>10</v>
+      </c>
+      <c r="D53" s="3">
+        <f t="shared" si="0"/>
+        <v>0.97590361445783136</v>
+      </c>
+      <c r="E53" s="3">
+        <f t="shared" si="1"/>
+        <v>415</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54" s="3">
+        <v>155</v>
+      </c>
+      <c r="C54" s="3">
+        <v>27</v>
+      </c>
+      <c r="D54" s="3">
+        <f t="shared" si="0"/>
+        <v>0.85164835164835162</v>
+      </c>
+      <c r="E54" s="3">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B55" s="3">
+        <v>189</v>
+      </c>
+      <c r="C55" s="3">
+        <v>4</v>
+      </c>
+      <c r="D55" s="3">
+        <f t="shared" si="0"/>
+        <v>0.97927461139896377</v>
+      </c>
+      <c r="E55" s="3">
+        <f t="shared" si="1"/>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56" s="3">
+        <v>536</v>
+      </c>
+      <c r="C56" s="3">
+        <v>3</v>
+      </c>
+      <c r="D56" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99443413729128016</v>
+      </c>
+      <c r="E56" s="3">
+        <f t="shared" si="1"/>
+        <v>539</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B57" s="3">
+        <v>424</v>
+      </c>
+      <c r="C57" s="3">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E57" s="3">
+        <f t="shared" si="1"/>
+        <v>424</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B58" s="3">
+        <v>575</v>
+      </c>
+      <c r="C58" s="3">
+        <v>2</v>
+      </c>
+      <c r="D58" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99653379549393417</v>
+      </c>
+      <c r="E58" s="3">
+        <f t="shared" si="1"/>
+        <v>577</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B59" s="3">
+        <v>167</v>
+      </c>
+      <c r="C59" s="3">
+        <v>4</v>
+      </c>
+      <c r="D59" s="3">
+        <f t="shared" si="0"/>
+        <v>0.97660818713450293</v>
+      </c>
+      <c r="E59" s="3">
+        <f t="shared" si="1"/>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B60" s="3">
+        <v>149</v>
+      </c>
+      <c r="C60" s="3">
+        <v>5</v>
+      </c>
+      <c r="D60" s="3">
+        <f t="shared" si="0"/>
+        <v>0.96753246753246758</v>
+      </c>
+      <c r="E60" s="3">
+        <f t="shared" si="1"/>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B61" s="3">
+        <v>518</v>
+      </c>
+      <c r="C61" s="3">
+        <v>2</v>
+      </c>
+      <c r="D61" s="3">
+        <f t="shared" si="0"/>
+        <v>0.99615384615384617</v>
+      </c>
+      <c r="E61" s="3">
+        <f t="shared" si="1"/>
+        <v>520</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B62" s="3">
+        <v>76</v>
+      </c>
+      <c r="C62" s="3">
+        <v>15</v>
+      </c>
+      <c r="D62" s="3">
+        <f t="shared" si="0"/>
+        <v>0.8351648351648352</v>
+      </c>
+      <c r="E62" s="3">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B63" s="3">
+        <v>84</v>
+      </c>
+      <c r="C63" s="3">
+        <v>10</v>
+      </c>
+      <c r="D63" s="3">
+        <f t="shared" si="0"/>
+        <v>0.8936170212765957</v>
+      </c>
+      <c r="E63" s="3">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B64" s="3">
+        <v>131</v>
+      </c>
+      <c r="C64" s="3">
+        <v>3</v>
+      </c>
+      <c r="D64" s="3">
+        <f t="shared" si="0"/>
+        <v>0.97761194029850751</v>
+      </c>
+      <c r="E64" s="3">
+        <f t="shared" si="1"/>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B65" s="3">
+        <v>249</v>
+      </c>
+      <c r="C65" s="3">
+        <v>92</v>
+      </c>
+      <c r="D65" s="3">
+        <f t="shared" si="0"/>
+        <v>0.73020527859237538</v>
+      </c>
+      <c r="E65" s="3">
+        <f t="shared" si="1"/>
+        <v>341</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B66" s="3">
+        <v>137</v>
+      </c>
+      <c r="C66" s="3">
+        <v>30</v>
+      </c>
+      <c r="D66" s="3">
+        <f t="shared" si="0"/>
+        <v>0.82035928143712578</v>
+      </c>
+      <c r="E66" s="3">
+        <f t="shared" si="1"/>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B67" s="3">
+        <v>334</v>
+      </c>
+      <c r="C67" s="3">
+        <v>1</v>
+      </c>
+      <c r="D67" s="3">
+        <f t="shared" ref="D67:D129" si="2">B67/(B67+C67)</f>
+        <v>0.9970149253731343</v>
+      </c>
+      <c r="E67" s="3">
+        <f t="shared" ref="E67:E129" si="3">B67+C67</f>
+        <v>335</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B68" s="3">
+        <v>213</v>
+      </c>
+      <c r="C68" s="3">
+        <v>1</v>
+      </c>
+      <c r="D68" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99532710280373837</v>
+      </c>
+      <c r="E68" s="3">
+        <f t="shared" si="3"/>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B69" s="3">
+        <v>751</v>
+      </c>
+      <c r="C69" s="3">
+        <v>33</v>
+      </c>
+      <c r="D69" s="3">
+        <f t="shared" si="2"/>
+        <v>0.95790816326530615</v>
+      </c>
+      <c r="E69" s="3">
+        <f t="shared" si="3"/>
+        <v>784</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B70" s="3">
+        <v>92</v>
+      </c>
+      <c r="C70" s="3">
+        <v>43</v>
+      </c>
+      <c r="D70" s="3">
+        <f t="shared" si="2"/>
+        <v>0.68148148148148147</v>
+      </c>
+      <c r="E70" s="3">
+        <f t="shared" si="3"/>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B71" s="3">
+        <v>123</v>
+      </c>
+      <c r="C71" s="3">
+        <v>77</v>
+      </c>
+      <c r="D71" s="3">
+        <f t="shared" si="2"/>
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="E71" s="3">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B72" s="3">
+        <v>194</v>
+      </c>
+      <c r="C72" s="3">
+        <v>2</v>
+      </c>
+      <c r="D72" s="3">
+        <f t="shared" si="2"/>
+        <v>0.98979591836734693</v>
+      </c>
+      <c r="E72" s="3">
+        <f t="shared" si="3"/>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B73" s="3">
+        <v>135</v>
+      </c>
+      <c r="C73" s="3">
+        <v>10</v>
+      </c>
+      <c r="D73" s="3">
+        <f t="shared" si="2"/>
+        <v>0.93103448275862066</v>
+      </c>
+      <c r="E73" s="3">
+        <f t="shared" si="3"/>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B74" s="3">
+        <v>134</v>
+      </c>
+      <c r="C74" s="3">
+        <v>37</v>
+      </c>
+      <c r="D74" s="3">
+        <f t="shared" si="2"/>
+        <v>0.783625730994152</v>
+      </c>
+      <c r="E74" s="3">
+        <f t="shared" si="3"/>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B75" s="3">
+        <v>84</v>
+      </c>
+      <c r="C75" s="3">
+        <v>1</v>
+      </c>
+      <c r="D75" s="3">
+        <f t="shared" si="2"/>
+        <v>0.9882352941176471</v>
+      </c>
+      <c r="E75" s="3">
+        <f t="shared" si="3"/>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B76" s="3">
+        <v>245</v>
+      </c>
+      <c r="C76" s="3">
+        <v>2</v>
+      </c>
+      <c r="D76" s="3">
+        <f t="shared" si="2"/>
+        <v>0.9919028340080972</v>
+      </c>
+      <c r="E76" s="3">
+        <f t="shared" si="3"/>
+        <v>247</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B77" s="3">
+        <v>322</v>
+      </c>
+      <c r="C77" s="3">
+        <v>2</v>
+      </c>
+      <c r="D77" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99382716049382713</v>
+      </c>
+      <c r="E77" s="3">
+        <f t="shared" si="3"/>
+        <v>324</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B78" s="3">
+        <v>185</v>
+      </c>
+      <c r="C78" s="3">
+        <v>9</v>
+      </c>
+      <c r="D78" s="3">
+        <f t="shared" si="2"/>
+        <v>0.95360824742268047</v>
+      </c>
+      <c r="E78" s="3">
+        <f t="shared" si="3"/>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B79" s="3">
+        <v>200</v>
+      </c>
+      <c r="C79" s="3">
+        <v>5</v>
+      </c>
+      <c r="D79" s="3">
+        <f t="shared" si="2"/>
+        <v>0.97560975609756095</v>
+      </c>
+      <c r="E79" s="3">
+        <f t="shared" si="3"/>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B80" s="3">
+        <v>118</v>
+      </c>
+      <c r="C80" s="3">
+        <v>46</v>
+      </c>
+      <c r="D80" s="3">
+        <f t="shared" si="2"/>
+        <v>0.71951219512195119</v>
+      </c>
+      <c r="E80" s="3">
+        <f t="shared" si="3"/>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B81" s="3">
+        <v>175</v>
+      </c>
+      <c r="C81" s="3">
+        <v>4</v>
+      </c>
+      <c r="D81" s="3">
+        <f t="shared" si="2"/>
+        <v>0.97765363128491622</v>
+      </c>
+      <c r="E81" s="3">
+        <f t="shared" si="3"/>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B82" s="3">
+        <v>198</v>
+      </c>
+      <c r="C82" s="3">
+        <v>36</v>
+      </c>
+      <c r="D82" s="3">
+        <f t="shared" si="2"/>
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="E82" s="3">
+        <f t="shared" si="3"/>
+        <v>234</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B83" s="3">
+        <v>31</v>
+      </c>
+      <c r="C83" s="3">
+        <v>95</v>
+      </c>
+      <c r="D83" s="3">
+        <f t="shared" si="2"/>
+        <v>0.24603174603174602</v>
+      </c>
+      <c r="E83" s="3">
+        <f t="shared" si="3"/>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B84" s="3">
+        <v>759</v>
+      </c>
+      <c r="C84" s="3">
+        <v>6</v>
+      </c>
+      <c r="D84" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99215686274509807</v>
+      </c>
+      <c r="E84" s="3">
+        <f t="shared" si="3"/>
+        <v>765</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B85" s="3">
+        <v>573</v>
+      </c>
+      <c r="C85" s="3">
+        <v>2</v>
+      </c>
+      <c r="D85" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99652173913043474</v>
+      </c>
+      <c r="E85" s="3">
+        <f t="shared" si="3"/>
+        <v>575</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B86" s="3">
+        <v>293</v>
+      </c>
+      <c r="C86" s="3">
+        <v>0</v>
+      </c>
+      <c r="D86" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E86" s="3">
+        <f t="shared" si="3"/>
+        <v>293</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B87" s="3">
+        <v>362</v>
+      </c>
+      <c r="C87" s="3">
+        <v>0</v>
+      </c>
+      <c r="D87" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E87" s="3">
+        <f t="shared" si="3"/>
+        <v>362</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B88" s="3">
+        <v>118</v>
+      </c>
+      <c r="C88" s="3">
+        <v>1</v>
+      </c>
+      <c r="D88" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99159663865546221</v>
+      </c>
+      <c r="E88" s="3">
+        <f t="shared" si="3"/>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B89" s="3">
+        <v>70</v>
+      </c>
+      <c r="C89" s="3">
+        <v>59</v>
+      </c>
+      <c r="D89" s="3">
+        <f t="shared" si="2"/>
+        <v>0.54263565891472865</v>
+      </c>
+      <c r="E89" s="3">
+        <f t="shared" si="3"/>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B90" s="3">
+        <v>48</v>
+      </c>
+      <c r="C90" s="3">
+        <v>0</v>
+      </c>
+      <c r="D90" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E90" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B91" s="3">
+        <v>90</v>
+      </c>
+      <c r="C91" s="3">
+        <v>5</v>
+      </c>
+      <c r="D91" s="3">
+        <f t="shared" si="2"/>
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="E91" s="3">
+        <f t="shared" si="3"/>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B92" s="3">
+        <v>149</v>
+      </c>
+      <c r="C92" s="3">
+        <v>0</v>
+      </c>
+      <c r="D92" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E92" s="3">
+        <f t="shared" si="3"/>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B93" s="3">
+        <v>1794</v>
+      </c>
+      <c r="C93" s="3">
+        <v>25</v>
+      </c>
+      <c r="D93" s="3">
+        <f t="shared" si="2"/>
+        <v>0.98625618471687737</v>
+      </c>
+      <c r="E93" s="3">
+        <f t="shared" si="3"/>
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B94" s="3">
+        <v>112</v>
+      </c>
+      <c r="C94" s="3">
+        <v>1</v>
+      </c>
+      <c r="D94" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99115044247787609</v>
+      </c>
+      <c r="E94" s="3">
+        <f t="shared" si="3"/>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B95" s="3">
+        <v>197</v>
+      </c>
+      <c r="C95" s="3">
+        <v>1</v>
+      </c>
+      <c r="D95" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99494949494949492</v>
+      </c>
+      <c r="E95" s="3">
+        <f t="shared" si="3"/>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B96" s="3">
+        <v>163</v>
+      </c>
+      <c r="C96" s="3">
+        <v>1</v>
+      </c>
+      <c r="D96" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99390243902439024</v>
+      </c>
+      <c r="E96" s="3">
+        <f t="shared" si="3"/>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B97" s="3">
+        <v>197</v>
+      </c>
+      <c r="C97" s="3">
+        <v>19</v>
+      </c>
+      <c r="D97" s="3">
+        <f t="shared" si="2"/>
+        <v>0.91203703703703709</v>
+      </c>
+      <c r="E97" s="3">
+        <f t="shared" si="3"/>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B98" s="3">
+        <v>730</v>
+      </c>
+      <c r="C98" s="3">
+        <v>32</v>
+      </c>
+      <c r="D98" s="3">
+        <f t="shared" si="2"/>
+        <v>0.95800524934383202</v>
+      </c>
+      <c r="E98" s="3">
+        <f t="shared" si="3"/>
+        <v>762</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B99" s="3">
+        <v>109</v>
+      </c>
+      <c r="C99" s="3">
+        <v>21</v>
+      </c>
+      <c r="D99" s="3">
+        <f t="shared" si="2"/>
+        <v>0.83846153846153848</v>
+      </c>
+      <c r="E99" s="3">
+        <f t="shared" si="3"/>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B100" s="3">
+        <v>573</v>
+      </c>
+      <c r="C100" s="3">
+        <v>6</v>
+      </c>
+      <c r="D100" s="3">
+        <f t="shared" si="2"/>
+        <v>0.98963730569948183</v>
+      </c>
+      <c r="E100" s="3">
+        <f t="shared" si="3"/>
+        <v>579</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B101" s="3">
+        <v>356</v>
+      </c>
+      <c r="C101" s="3">
+        <v>3</v>
+      </c>
+      <c r="D101" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99164345403899723</v>
+      </c>
+      <c r="E101" s="3">
+        <f t="shared" si="3"/>
+        <v>359</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B102" s="3">
+        <v>238</v>
+      </c>
+      <c r="C102" s="3">
+        <v>21</v>
+      </c>
+      <c r="D102" s="3">
+        <f t="shared" si="2"/>
+        <v>0.91891891891891897</v>
+      </c>
+      <c r="E102" s="3">
+        <f t="shared" si="3"/>
+        <v>259</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B103" s="3">
+        <v>1399</v>
+      </c>
+      <c r="C103" s="3">
+        <v>1</v>
+      </c>
+      <c r="D103" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99928571428571433</v>
+      </c>
+      <c r="E103" s="3">
+        <f t="shared" si="3"/>
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B104" s="3">
+        <v>142</v>
+      </c>
+      <c r="C104" s="3">
+        <v>0</v>
+      </c>
+      <c r="D104" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E104" s="3">
+        <f t="shared" si="3"/>
+        <v>142</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B105" s="3">
+        <v>156</v>
+      </c>
+      <c r="C105" s="3">
+        <v>17</v>
+      </c>
+      <c r="D105" s="3">
+        <f t="shared" si="2"/>
+        <v>0.90173410404624277</v>
+      </c>
+      <c r="E105" s="3">
+        <f t="shared" si="3"/>
+        <v>173</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B106" s="3">
+        <v>901</v>
+      </c>
+      <c r="C106" s="3">
+        <v>18</v>
+      </c>
+      <c r="D106" s="3">
+        <f t="shared" si="2"/>
+        <v>0.98041349292709468</v>
+      </c>
+      <c r="E106" s="3">
+        <f t="shared" si="3"/>
+        <v>919</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B107" s="3">
+        <v>133</v>
+      </c>
+      <c r="C107" s="3">
+        <v>0</v>
+      </c>
+      <c r="D107" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E107" s="3">
+        <f t="shared" si="3"/>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B108" s="3">
+        <v>120</v>
+      </c>
+      <c r="C108" s="3">
+        <v>23</v>
+      </c>
+      <c r="D108" s="3">
+        <f t="shared" si="2"/>
+        <v>0.83916083916083917</v>
+      </c>
+      <c r="E108" s="3">
+        <f t="shared" si="3"/>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B109" s="3">
+        <v>454</v>
+      </c>
+      <c r="C109" s="3">
+        <v>62</v>
+      </c>
+      <c r="D109" s="3">
+        <f t="shared" si="2"/>
+        <v>0.87984496124031009</v>
+      </c>
+      <c r="E109" s="3">
+        <f t="shared" si="3"/>
+        <v>516</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B110" s="3">
+        <v>772</v>
+      </c>
+      <c r="C110" s="3">
+        <v>4</v>
+      </c>
+      <c r="D110" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99484536082474229</v>
+      </c>
+      <c r="E110" s="3">
+        <f t="shared" si="3"/>
+        <v>776</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B111" s="3">
+        <v>327</v>
+      </c>
+      <c r="C111" s="3">
+        <v>152</v>
+      </c>
+      <c r="D111" s="3">
+        <f t="shared" si="2"/>
+        <v>0.68267223382045927</v>
+      </c>
+      <c r="E111" s="3">
+        <f t="shared" si="3"/>
+        <v>479</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B112" s="3">
+        <v>166</v>
+      </c>
+      <c r="C112" s="3">
+        <v>151</v>
+      </c>
+      <c r="D112" s="3">
+        <f t="shared" si="2"/>
+        <v>0.52365930599369082</v>
+      </c>
+      <c r="E112" s="3">
+        <f t="shared" si="3"/>
+        <v>317</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B113" s="3">
+        <v>143</v>
+      </c>
+      <c r="C113" s="3">
+        <v>23</v>
+      </c>
+      <c r="D113" s="3">
+        <f t="shared" si="2"/>
+        <v>0.86144578313253017</v>
+      </c>
+      <c r="E113" s="3">
+        <f t="shared" si="3"/>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B114" s="3">
+        <v>166</v>
+      </c>
+      <c r="C114" s="3">
+        <v>3</v>
+      </c>
+      <c r="D114" s="3">
+        <f t="shared" si="2"/>
+        <v>0.98224852071005919</v>
+      </c>
+      <c r="E114" s="3">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B115" s="3">
+        <v>201</v>
+      </c>
+      <c r="C115" s="3">
+        <v>39</v>
+      </c>
+      <c r="D115" s="3">
+        <f t="shared" si="2"/>
+        <v>0.83750000000000002</v>
+      </c>
+      <c r="E115" s="3">
+        <f t="shared" si="3"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B116" s="3">
+        <v>98</v>
+      </c>
+      <c r="C116" s="3">
+        <v>66</v>
+      </c>
+      <c r="D116" s="3">
+        <f t="shared" si="2"/>
+        <v>0.59756097560975607</v>
+      </c>
+      <c r="E116" s="3">
+        <f t="shared" si="3"/>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B117" s="3">
+        <v>181</v>
+      </c>
+      <c r="C117" s="3">
+        <v>6</v>
+      </c>
+      <c r="D117" s="3">
+        <f t="shared" si="2"/>
+        <v>0.96791443850267378</v>
+      </c>
+      <c r="E117" s="3">
+        <f t="shared" si="3"/>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B118" s="3">
+        <v>162</v>
+      </c>
+      <c r="C118" s="3">
+        <v>42</v>
+      </c>
+      <c r="D118" s="3">
+        <f t="shared" si="2"/>
+        <v>0.79411764705882348</v>
+      </c>
+      <c r="E118" s="3">
+        <f t="shared" si="3"/>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B119" s="3">
+        <v>179</v>
+      </c>
+      <c r="C119" s="3">
+        <v>20</v>
+      </c>
+      <c r="D119" s="3">
+        <f t="shared" si="2"/>
+        <v>0.89949748743718594</v>
+      </c>
+      <c r="E119" s="3">
+        <f t="shared" si="3"/>
+        <v>199</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B120" s="3">
+        <v>190</v>
+      </c>
+      <c r="C120" s="3">
+        <v>1</v>
+      </c>
+      <c r="D120" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99476439790575921</v>
+      </c>
+      <c r="E120" s="3">
+        <f t="shared" si="3"/>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B121" s="3">
+        <v>178</v>
+      </c>
+      <c r="C121" s="3">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E121" s="3">
+        <f t="shared" si="3"/>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B122" s="3">
+        <v>224</v>
+      </c>
+      <c r="C122" s="3">
+        <v>1</v>
+      </c>
+      <c r="D122" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99555555555555553</v>
+      </c>
+      <c r="E122" s="3">
+        <f t="shared" si="3"/>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B123" s="3">
+        <v>231</v>
+      </c>
+      <c r="C123" s="3">
+        <v>7</v>
+      </c>
+      <c r="D123" s="3">
+        <f t="shared" si="2"/>
+        <v>0.97058823529411764</v>
+      </c>
+      <c r="E123" s="3">
+        <f t="shared" si="3"/>
+        <v>238</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B124" s="3">
+        <v>156</v>
+      </c>
+      <c r="C124" s="3">
+        <v>10</v>
+      </c>
+      <c r="D124" s="3">
+        <f t="shared" si="2"/>
+        <v>0.93975903614457834</v>
+      </c>
+      <c r="E124" s="3">
+        <f t="shared" si="3"/>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B125" s="3">
+        <v>125</v>
+      </c>
+      <c r="C125" s="3">
+        <v>7</v>
+      </c>
+      <c r="D125" s="3">
+        <f t="shared" si="2"/>
+        <v>0.94696969696969702</v>
+      </c>
+      <c r="E125" s="3">
+        <f t="shared" si="3"/>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B126" s="3">
+        <v>1883</v>
+      </c>
+      <c r="C126" s="3">
+        <v>6</v>
+      </c>
+      <c r="D126" s="3">
+        <f t="shared" si="2"/>
+        <v>0.99682371625198518</v>
+      </c>
+      <c r="E126" s="3">
+        <f t="shared" si="3"/>
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B127" s="3">
+        <v>350</v>
+      </c>
+      <c r="C127" s="3">
+        <v>4</v>
+      </c>
+      <c r="D127" s="3">
+        <f t="shared" si="2"/>
+        <v>0.98870056497175141</v>
+      </c>
+      <c r="E127" s="3">
+        <f t="shared" si="3"/>
+        <v>354</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B128" s="3">
+        <v>126</v>
+      </c>
+      <c r="C128" s="3">
+        <v>15</v>
+      </c>
+      <c r="D128" s="3">
+        <f t="shared" si="2"/>
+        <v>0.8936170212765957</v>
+      </c>
+      <c r="E128" s="3">
+        <f t="shared" si="3"/>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B129" s="3">
+        <v>319</v>
+      </c>
+      <c r="C129" s="3">
+        <v>10</v>
+      </c>
+      <c r="D129" s="3">
+        <f t="shared" si="2"/>
+        <v>0.96960486322188455</v>
+      </c>
+      <c r="E129" s="3">
+        <f t="shared" si="3"/>
+        <v>329</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>